--- a/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
+++ b/Cursor/3_쿠팡 모니터링/cp_payment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Cursor/3_쿠팡 모니터링/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Cursor/coupang-monitoring-vercel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07F7F3F-0555-D744-A120-78EA0FEA8DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAEFE6-93A9-6C41-AAA1-DBCAFFEF3144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주요지표" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="831">
   <si>
     <t>와이즈앱/리테일</t>
   </si>
@@ -2634,6 +2634,51 @@
   <si>
     <t>WoW</t>
     <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>+37.4%</t>
+  </si>
+  <si>
+    <t>+37.5%</t>
+  </si>
+  <si>
+    <t>+42.4%</t>
+  </si>
+  <si>
+    <t>+35.4%</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>-23.4%</t>
+  </si>
+  <si>
+    <t>-16.9%</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>+33.0%</t>
   </si>
 </sst>
 </file>
@@ -2978,10 +3023,22 @@
     <xf numFmtId="42" fontId="3" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2992,18 +3049,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3321,40 +3366,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R263"/>
+  <dimension ref="A1:R271"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="22" customHeight="1"/>
   <cols>
     <col min="1" max="15" width="15.83203125" customWidth="1"/>
-    <col min="16" max="16" width="11" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.1640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" style="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.6640625" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" ht="17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+    </row>
+    <row r="2" spans="1:18" ht="17">
       <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
@@ -3368,56 +3413,56 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:18" ht="17">
+      <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+    </row>
+    <row r="4" spans="1:18" ht="17">
+      <c r="A4" s="21"/>
+      <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="24" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="23" t="s">
         <v>815</v>
       </c>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="18"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+    </row>
+    <row r="5" spans="1:18" ht="17">
+      <c r="A5" s="21"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -3460,17 +3505,17 @@
       <c r="O5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P5" s="25" t="s">
+      <c r="P5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="25" t="s">
+      <c r="R5" s="19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" ht="17">
       <c r="A6" s="12" t="s">
         <v>790</v>
       </c>
@@ -3516,20 +3561,20 @@
       <c r="O6" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="P6" s="26" t="e">
+      <c r="P6" s="20" t="e">
         <f>(B6-#REF!)/#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="Q6" s="26" t="e">
+      <c r="Q6" s="20" t="e">
         <f>(E6-#REF!)/#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="R6" s="26" t="e">
+      <c r="R6" s="20" t="e">
         <f>(F6-#REF!)/#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" ht="17">
       <c r="A7" s="12" t="s">
         <v>791</v>
       </c>
@@ -3575,20 +3620,20 @@
       <c r="O7" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="P7" s="26" t="e">
+      <c r="P7" s="20" t="e">
         <f>(B7-#REF!)/#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="Q7" s="26" t="e">
+      <c r="Q7" s="20" t="e">
         <f>(E7-#REF!)/#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="R7" s="26" t="e">
+      <c r="R7" s="20" t="e">
         <f>(F7-#REF!)/#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" ht="17">
       <c r="A8" s="12" t="s">
         <v>792</v>
       </c>
@@ -3634,20 +3679,20 @@
       <c r="O8" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="P8" s="26" t="e">
+      <c r="P8" s="20" t="e">
         <f t="shared" ref="P8:P71" si="0">(B8-B1)/B1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Q8" s="26" t="e">
+      <c r="Q8" s="20" t="e">
         <f t="shared" ref="Q8:Q12" si="1">(E8-E1)/E1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R8" s="26" t="e">
+      <c r="R8" s="20" t="e">
         <f t="shared" ref="R8:R12" si="2">(F8-F1)/F1</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" ht="17">
       <c r="A9" s="12" t="s">
         <v>794</v>
       </c>
@@ -3693,20 +3738,20 @@
       <c r="O9" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="P9" s="26" t="e">
+      <c r="P9" s="20" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q9" s="26" t="e">
+      <c r="Q9" s="20" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R9" s="26" t="e">
+      <c r="R9" s="20" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" ht="17">
       <c r="A10" s="12" t="s">
         <v>798</v>
       </c>
@@ -3752,20 +3797,20 @@
       <c r="O10" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="P10" s="26" t="e">
+      <c r="P10" s="20" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q10" s="26" t="e">
+      <c r="Q10" s="20" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R10" s="26" t="e">
+      <c r="R10" s="20" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" ht="17">
       <c r="A11" s="12" t="s">
         <v>800</v>
       </c>
@@ -3811,20 +3856,20 @@
       <c r="O11" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="P11" s="26" t="e">
+      <c r="P11" s="20" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q11" s="26" t="e">
+      <c r="Q11" s="20" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R11" s="26" t="e">
+      <c r="R11" s="20" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" ht="17">
       <c r="A12" s="12" t="s">
         <v>802</v>
       </c>
@@ -3870,20 +3915,20 @@
       <c r="O12" s="15" t="s">
         <v>559</v>
       </c>
-      <c r="P12" s="26" t="e">
+      <c r="P12" s="20" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q12" s="26" t="e">
+      <c r="Q12" s="20" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R12" s="26" t="e">
+      <c r="R12" s="20" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" ht="17">
       <c r="A13" s="12" t="s">
         <v>803</v>
       </c>
@@ -3929,20 +3974,20 @@
       <c r="O13" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="P13" s="26">
+      <c r="P13" s="20">
         <f t="shared" si="0"/>
         <v>-0.13078450470355382</v>
       </c>
-      <c r="Q13" s="26">
+      <c r="Q13" s="20">
         <f>(E13-E6)/E6</f>
         <v>-3.9262989471128669E-2</v>
       </c>
-      <c r="R13" s="26">
+      <c r="R13" s="20">
         <f>(F13-F6)/F6</f>
         <v>-4.9576136731741362E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" ht="17">
       <c r="A14" s="12" t="s">
         <v>805</v>
       </c>
@@ -3988,20 +4033,20 @@
       <c r="O14" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="P14" s="26">
+      <c r="P14" s="20">
         <f t="shared" si="0"/>
         <v>-9.9824598000889386E-2</v>
       </c>
-      <c r="Q14" s="26">
+      <c r="Q14" s="20">
         <f t="shared" ref="Q14:Q77" si="3">(E14-E7)/E7</f>
         <v>-3.5224704681979545E-2</v>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="20">
         <f t="shared" ref="R14:R77" si="4">(F14-F7)/F7</f>
         <v>-4.8931555672281732E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" ht="17">
       <c r="A15" s="12" t="s">
         <v>806</v>
       </c>
@@ -4047,20 +4092,20 @@
       <c r="O15" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="P15" s="26">
+      <c r="P15" s="20">
         <f t="shared" si="0"/>
         <v>-5.4274762800283906E-2</v>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="20">
         <f t="shared" si="3"/>
         <v>8.8008256074937653E-3</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="20">
         <f t="shared" si="4"/>
         <v>-1.4378684476480058E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" ht="17">
       <c r="A16" s="12" t="s">
         <v>807</v>
       </c>
@@ -4106,20 +4151,20 @@
       <c r="O16" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="P16" s="26">
+      <c r="P16" s="20">
         <f t="shared" si="0"/>
         <v>-3.4612854724394015E-2</v>
       </c>
-      <c r="Q16" s="26">
+      <c r="Q16" s="20">
         <f t="shared" si="3"/>
         <v>-2.0606200471824439E-2</v>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="20">
         <f t="shared" si="4"/>
         <v>-1.4381173736199885E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" ht="17">
       <c r="A17" s="12" t="s">
         <v>810</v>
       </c>
@@ -4165,20 +4210,20 @@
       <c r="O17" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="P17" s="26">
+      <c r="P17" s="20">
         <f t="shared" si="0"/>
         <v>-2.8972803093979264E-2</v>
       </c>
-      <c r="Q17" s="26">
+      <c r="Q17" s="20">
         <f t="shared" si="3"/>
         <v>-3.3372219220236844E-2</v>
       </c>
-      <c r="R17" s="26">
+      <c r="R17" s="20">
         <f t="shared" si="4"/>
         <v>-2.9181971093327996E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" ht="17">
       <c r="A18" s="12" t="s">
         <v>811</v>
       </c>
@@ -4224,20 +4269,20 @@
       <c r="O18" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="P18" s="26">
+      <c r="P18" s="20">
         <f t="shared" si="0"/>
         <v>-2.7248732704455839E-2</v>
       </c>
-      <c r="Q18" s="26">
+      <c r="Q18" s="20">
         <f t="shared" si="3"/>
         <v>-4.3798145030765956E-2</v>
       </c>
-      <c r="R18" s="26">
+      <c r="R18" s="20">
         <f t="shared" si="4"/>
         <v>-4.2866046015887192E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" ht="17">
       <c r="A19" s="12" t="s">
         <v>812</v>
       </c>
@@ -4283,20 +4328,20 @@
       <c r="O19" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="P19" s="26">
+      <c r="P19" s="20">
         <f t="shared" si="0"/>
         <v>-8.7240367217895062E-2</v>
       </c>
-      <c r="Q19" s="26">
+      <c r="Q19" s="20">
         <f t="shared" si="3"/>
         <v>-7.7853520249949279E-2</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="20">
         <f t="shared" si="4"/>
         <v>-5.8386489959590643E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" ht="17">
       <c r="A20" s="12" t="s">
         <v>735</v>
       </c>
@@ -4342,20 +4387,20 @@
       <c r="O20" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="P20" s="26">
+      <c r="P20" s="20">
         <f t="shared" si="0"/>
         <v>-9.7216520655897878E-2</v>
       </c>
-      <c r="Q20" s="26">
+      <c r="Q20" s="20">
         <f t="shared" si="3"/>
         <v>-0.11908617928817737</v>
       </c>
-      <c r="R20" s="26">
+      <c r="R20" s="20">
         <f t="shared" si="4"/>
         <v>-8.8265021631567325E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" ht="17">
       <c r="A21" s="12" t="s">
         <v>737</v>
       </c>
@@ -4401,20 +4446,20 @@
       <c r="O21" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="P21" s="26">
+      <c r="P21" s="20">
         <f t="shared" si="0"/>
         <v>-9.7521514495384015E-2</v>
       </c>
-      <c r="Q21" s="26">
+      <c r="Q21" s="20">
         <f t="shared" si="3"/>
         <v>-0.10385041404401589</v>
       </c>
-      <c r="R21" s="26">
+      <c r="R21" s="20">
         <f t="shared" si="4"/>
         <v>-7.1461003428372152E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" ht="17">
       <c r="A22" s="12" t="s">
         <v>739</v>
       </c>
@@ -4460,20 +4505,20 @@
       <c r="O22" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="P22" s="26">
+      <c r="P22" s="20">
         <f t="shared" si="0"/>
         <v>-0.14233925395930228</v>
       </c>
-      <c r="Q22" s="26">
+      <c r="Q22" s="20">
         <f t="shared" si="3"/>
         <v>-0.13691452228494302</v>
       </c>
-      <c r="R22" s="26">
+      <c r="R22" s="20">
         <f t="shared" si="4"/>
         <v>-0.10334655809467724</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" ht="17">
       <c r="A23" s="12" t="s">
         <v>741</v>
       </c>
@@ -4519,20 +4564,20 @@
       <c r="O23" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="P23" s="26">
+      <c r="P23" s="20">
         <f t="shared" si="0"/>
         <v>-9.9587113106970743E-2</v>
       </c>
-      <c r="Q23" s="26">
+      <c r="Q23" s="20">
         <f t="shared" si="3"/>
         <v>-6.8834997431069744E-2</v>
       </c>
-      <c r="R23" s="26">
+      <c r="R23" s="20">
         <f t="shared" si="4"/>
         <v>-6.3275783993910401E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" ht="17">
       <c r="A24" s="12" t="s">
         <v>743</v>
       </c>
@@ -4578,20 +4623,20 @@
       <c r="O24" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="P24" s="26">
+      <c r="P24" s="20">
         <f t="shared" si="0"/>
         <v>-7.5751487429462541E-2</v>
       </c>
-      <c r="Q24" s="26">
+      <c r="Q24" s="20">
         <f t="shared" si="3"/>
         <v>-2.0590307324825363E-2</v>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="20">
         <f t="shared" si="4"/>
         <v>-1.5429861784374364E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" ht="17">
       <c r="A25" s="12" t="s">
         <v>745</v>
       </c>
@@ -4637,20 +4682,20 @@
       <c r="O25" s="15" t="s">
         <v>600</v>
       </c>
-      <c r="P25" s="26">
+      <c r="P25" s="20">
         <f t="shared" si="0"/>
         <v>-6.5865305959972226E-2</v>
       </c>
-      <c r="Q25" s="26">
+      <c r="Q25" s="20">
         <f t="shared" si="3"/>
         <v>-1.3526012410531064E-2</v>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="20">
         <f t="shared" si="4"/>
         <v>-5.3617072023426993E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" ht="17">
       <c r="A26" s="12" t="s">
         <v>746</v>
       </c>
@@ -4696,20 +4741,20 @@
       <c r="O26" s="15" t="s">
         <v>749</v>
       </c>
-      <c r="P26" s="26">
+      <c r="P26" s="20">
         <f t="shared" si="0"/>
         <v>-3.0813752289037795E-3</v>
       </c>
-      <c r="Q26" s="26">
+      <c r="Q26" s="20">
         <f t="shared" si="3"/>
         <v>-3.5305656666925395E-2</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="20">
         <f t="shared" si="4"/>
         <v>-1.3176864349319816E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" ht="17">
       <c r="A27" s="12" t="s">
         <v>750</v>
       </c>
@@ -4755,20 +4800,20 @@
       <c r="O27" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="P27" s="26">
+      <c r="P27" s="20">
         <f t="shared" si="0"/>
         <v>-2.2519781515335988E-2</v>
       </c>
-      <c r="Q27" s="26">
+      <c r="Q27" s="20">
         <f t="shared" si="3"/>
         <v>1.4246681796852831E-2</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="20">
         <f t="shared" si="4"/>
         <v>1.6931459433652613E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" ht="17">
       <c r="A28" s="12" t="s">
         <v>752</v>
       </c>
@@ -4814,20 +4859,20 @@
       <c r="O28" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="P28" s="26">
+      <c r="P28" s="20">
         <f t="shared" si="0"/>
         <v>1.0585255510954655E-2</v>
       </c>
-      <c r="Q28" s="26">
+      <c r="Q28" s="20">
         <f t="shared" si="3"/>
         <v>2.1457102218641142E-2</v>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="20">
         <f t="shared" si="4"/>
         <v>2.1705566381000428E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" ht="17">
       <c r="A29" s="12" t="s">
         <v>753</v>
       </c>
@@ -4873,20 +4918,20 @@
       <c r="O29" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="P29" s="26">
+      <c r="P29" s="20">
         <f t="shared" si="0"/>
         <v>3.0076391783361387E-2</v>
       </c>
-      <c r="Q29" s="26">
+      <c r="Q29" s="20">
         <f t="shared" si="3"/>
         <v>4.8859355082925313E-2</v>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="20">
         <f t="shared" si="4"/>
         <v>3.8965932699587452E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" ht="17">
       <c r="A30" s="12" t="s">
         <v>756</v>
       </c>
@@ -4932,20 +4977,20 @@
       <c r="O30" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="P30" s="26">
+      <c r="P30" s="20">
         <f t="shared" si="0"/>
         <v>5.7042350653567372E-2</v>
       </c>
-      <c r="Q30" s="26">
+      <c r="Q30" s="20">
         <f t="shared" si="3"/>
         <v>6.7163419560712659E-2</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="20">
         <f t="shared" si="4"/>
         <v>7.0268649164544172E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" ht="17">
       <c r="A31" s="12" t="s">
         <v>758</v>
       </c>
@@ -4991,20 +5036,20 @@
       <c r="O31" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="P31" s="26">
+      <c r="P31" s="20">
         <f t="shared" si="0"/>
         <v>2.9527479172399871E-2</v>
       </c>
-      <c r="Q31" s="26">
+      <c r="Q31" s="20">
         <f t="shared" si="3"/>
         <v>1.8739717612355773E-2</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="20">
         <f t="shared" si="4"/>
         <v>9.2244270980281519E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" ht="17">
       <c r="A32" s="12" t="s">
         <v>760</v>
       </c>
@@ -5050,20 +5095,20 @@
       <c r="O32" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="P32" s="26">
+      <c r="P32" s="20">
         <f t="shared" si="0"/>
         <v>2.0764646024865621E-2</v>
       </c>
-      <c r="Q32" s="26">
+      <c r="Q32" s="20">
         <f t="shared" si="3"/>
         <v>1.3626254950489847E-2</v>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="20">
         <f t="shared" si="4"/>
         <v>7.9638856834700485E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" ht="17">
       <c r="A33" s="12" t="s">
         <v>762</v>
       </c>
@@ -5109,20 +5154,20 @@
       <c r="O33" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="P33" s="26">
+      <c r="P33" s="20">
         <f t="shared" si="0"/>
         <v>-1.0494219847630474E-2</v>
       </c>
-      <c r="Q33" s="26">
+      <c r="Q33" s="20">
         <f t="shared" si="3"/>
         <v>-6.4309185655324203E-3</v>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="20">
         <f t="shared" si="4"/>
         <v>-3.8936060855501047E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:18" ht="17">
       <c r="A34" s="12" t="s">
         <v>763</v>
       </c>
@@ -5168,20 +5213,20 @@
       <c r="O34" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="P34" s="26">
+      <c r="P34" s="20">
         <f t="shared" si="0"/>
         <v>-1.307283357666118E-2</v>
       </c>
-      <c r="Q34" s="26">
+      <c r="Q34" s="20">
         <f t="shared" si="3"/>
         <v>-3.4843715832005663E-2</v>
       </c>
-      <c r="R34" s="26">
+      <c r="R34" s="20">
         <f t="shared" si="4"/>
         <v>-2.4173642910076471E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:18" ht="17">
       <c r="A35" s="12" t="s">
         <v>765</v>
       </c>
@@ -5227,20 +5272,20 @@
       <c r="O35" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="P35" s="26">
+      <c r="P35" s="20">
         <f t="shared" si="0"/>
         <v>-5.8631709816542414E-2</v>
       </c>
-      <c r="Q35" s="26">
+      <c r="Q35" s="20">
         <f t="shared" si="3"/>
         <v>-8.9260217397102132E-2</v>
       </c>
-      <c r="R35" s="26">
+      <c r="R35" s="20">
         <f t="shared" si="4"/>
         <v>-8.2380674495052333E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:18" ht="17">
       <c r="A36" s="12" t="s">
         <v>766</v>
       </c>
@@ -5286,20 +5331,20 @@
       <c r="O36" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="P36" s="26">
+      <c r="P36" s="20">
         <f t="shared" si="0"/>
         <v>-3.8651394037955068E-2</v>
       </c>
-      <c r="Q36" s="26">
+      <c r="Q36" s="20">
         <f t="shared" si="3"/>
         <v>-7.0165296017390563E-2</v>
       </c>
-      <c r="R36" s="26">
+      <c r="R36" s="20">
         <f t="shared" si="4"/>
         <v>-4.4567506471855013E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:18" ht="17">
       <c r="A37" s="12" t="s">
         <v>769</v>
       </c>
@@ -5345,20 +5390,20 @@
       <c r="O37" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="P37" s="26">
+      <c r="P37" s="20">
         <f t="shared" si="0"/>
         <v>0.20778250749479876</v>
       </c>
-      <c r="Q37" s="26">
+      <c r="Q37" s="20">
         <f t="shared" si="3"/>
         <v>-4.9234164076972106E-2</v>
       </c>
-      <c r="R37" s="26">
+      <c r="R37" s="20">
         <f t="shared" si="4"/>
         <v>-4.594642312646964E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:18" ht="17">
       <c r="A38" s="12" t="s">
         <v>770</v>
       </c>
@@ -5404,20 +5449,20 @@
       <c r="O38" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="P38" s="26">
+      <c r="P38" s="20">
         <f t="shared" si="0"/>
         <v>8.9719178198298916E-2</v>
       </c>
-      <c r="Q38" s="26">
+      <c r="Q38" s="20">
         <f t="shared" si="3"/>
         <v>-1.004917559606888E-2</v>
       </c>
-      <c r="R38" s="26">
+      <c r="R38" s="20">
         <f t="shared" si="4"/>
         <v>-1.2064141662349362E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:18" ht="17">
       <c r="A39" s="12" t="s">
         <v>772</v>
       </c>
@@ -5463,20 +5508,20 @@
       <c r="O39" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="P39" s="26">
+      <c r="P39" s="20">
         <f t="shared" si="0"/>
         <v>0.27282758257990258</v>
       </c>
-      <c r="Q39" s="26">
+      <c r="Q39" s="20">
         <f t="shared" si="3"/>
         <v>-4.4685588967305054E-2</v>
       </c>
-      <c r="R39" s="26">
+      <c r="R39" s="20">
         <f t="shared" si="4"/>
         <v>-3.2279586026449196E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:18" ht="17">
       <c r="A40" s="12" t="s">
         <v>773</v>
       </c>
@@ -5522,20 +5567,20 @@
       <c r="O40" s="15" t="s">
         <v>749</v>
       </c>
-      <c r="P40" s="26">
+      <c r="P40" s="20">
         <f t="shared" si="0"/>
         <v>0.37656692799103031</v>
       </c>
-      <c r="Q40" s="26">
+      <c r="Q40" s="20">
         <f t="shared" si="3"/>
         <v>-1.8733580510225268E-2</v>
       </c>
-      <c r="R40" s="26">
+      <c r="R40" s="20">
         <f t="shared" si="4"/>
         <v>-2.7973715965339346E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:18" ht="17">
       <c r="A41" s="12" t="s">
         <v>774</v>
       </c>
@@ -5581,20 +5626,20 @@
       <c r="O41" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="P41" s="26">
+      <c r="P41" s="20">
         <f t="shared" si="0"/>
         <v>4.6297094971619809E-2</v>
       </c>
-      <c r="Q41" s="26">
+      <c r="Q41" s="20">
         <f t="shared" si="3"/>
         <v>6.2383241610763683E-3</v>
       </c>
-      <c r="R41" s="26">
+      <c r="R41" s="20">
         <f t="shared" si="4"/>
         <v>8.7321075988099311E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:18" ht="17">
       <c r="A42" s="12" t="s">
         <v>776</v>
       </c>
@@ -5640,20 +5685,20 @@
       <c r="O42" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="P42" s="26">
+      <c r="P42" s="20">
         <f t="shared" si="0"/>
         <v>0.12159953209151031</v>
       </c>
-      <c r="Q42" s="26">
+      <c r="Q42" s="20">
         <f t="shared" si="3"/>
         <v>5.0682025373392073E-2</v>
       </c>
-      <c r="R42" s="26">
+      <c r="R42" s="20">
         <f t="shared" si="4"/>
         <v>5.1708462232755312E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:18" ht="17">
       <c r="A43" s="12" t="s">
         <v>777</v>
       </c>
@@ -5699,20 +5744,20 @@
       <c r="O43" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="P43" s="26">
+      <c r="P43" s="20">
         <f t="shared" si="0"/>
         <v>-0.28952817055815983</v>
       </c>
-      <c r="Q43" s="26">
+      <c r="Q43" s="20">
         <f t="shared" si="3"/>
         <v>2.7489837866735489E-2</v>
       </c>
-      <c r="R43" s="26">
+      <c r="R43" s="20">
         <f t="shared" si="4"/>
         <v>1.4767446202098399E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:18" ht="17">
       <c r="A44" s="12" t="s">
         <v>778</v>
       </c>
@@ -5758,20 +5803,20 @@
       <c r="O44" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="P44" s="26">
+      <c r="P44" s="20">
         <f t="shared" si="0"/>
         <v>-0.11474176299543018</v>
       </c>
-      <c r="Q44" s="26">
+      <c r="Q44" s="20">
         <f t="shared" si="3"/>
         <v>-3.6149611299396596E-2</v>
       </c>
-      <c r="R44" s="26">
+      <c r="R44" s="20">
         <f t="shared" si="4"/>
         <v>-3.0311445950278619E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:18">
+    <row r="45" spans="1:18" ht="17">
       <c r="A45" s="12" t="s">
         <v>781</v>
       </c>
@@ -5817,20 +5862,20 @@
       <c r="O45" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="P45" s="26">
+      <c r="P45" s="20">
         <f t="shared" si="0"/>
         <v>-9.0804405462538637E-2</v>
       </c>
-      <c r="Q45" s="26">
+      <c r="Q45" s="20">
         <f t="shared" si="3"/>
         <v>-5.6842128823506727E-2</v>
       </c>
-      <c r="R45" s="26">
+      <c r="R45" s="20">
         <f t="shared" si="4"/>
         <v>-4.0160914280580939E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:18" ht="17">
       <c r="A46" s="12" t="s">
         <v>783</v>
       </c>
@@ -5876,20 +5921,20 @@
       <c r="O46" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="P46" s="26">
+      <c r="P46" s="20">
         <f t="shared" si="0"/>
         <v>-3.1511268477063939E-2</v>
       </c>
-      <c r="Q46" s="26">
+      <c r="Q46" s="20">
         <f t="shared" si="3"/>
         <v>-4.3793848852616548E-3</v>
       </c>
-      <c r="R46" s="26">
+      <c r="R46" s="20">
         <f t="shared" si="4"/>
         <v>1.5026407632160585E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:18" ht="17">
       <c r="A47" s="12" t="s">
         <v>785</v>
       </c>
@@ -5935,20 +5980,20 @@
       <c r="O47" s="15" t="s">
         <v>786</v>
       </c>
-      <c r="P47" s="26">
+      <c r="P47" s="20">
         <f t="shared" si="0"/>
         <v>-9.7545226494006685E-3</v>
       </c>
-      <c r="Q47" s="26">
+      <c r="Q47" s="20">
         <f t="shared" si="3"/>
         <v>1.6496020989479538E-3</v>
       </c>
-      <c r="R47" s="26">
+      <c r="R47" s="20">
         <f t="shared" si="4"/>
         <v>2.0592009518271358E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
+    <row r="48" spans="1:18" ht="17">
       <c r="A48" s="12" t="s">
         <v>787</v>
       </c>
@@ -5994,20 +6039,20 @@
       <c r="O48" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="P48" s="26">
+      <c r="P48" s="20">
         <f t="shared" si="0"/>
         <v>-3.4004342008129761E-2</v>
       </c>
-      <c r="Q48" s="26">
+      <c r="Q48" s="20">
         <f t="shared" si="3"/>
         <v>-2.873655109606733E-2</v>
       </c>
-      <c r="R48" s="26">
+      <c r="R48" s="20">
         <f t="shared" si="4"/>
         <v>-2.0559511351690173E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:18">
+    <row r="49" spans="1:18" ht="17">
       <c r="A49" s="12" t="s">
         <v>788</v>
       </c>
@@ -6053,20 +6098,20 @@
       <c r="O49" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="P49" s="26">
+      <c r="P49" s="20">
         <f t="shared" si="0"/>
         <v>-5.6352712161281668E-2</v>
       </c>
-      <c r="Q49" s="26">
+      <c r="Q49" s="20">
         <f t="shared" si="3"/>
         <v>-4.4625643882583908E-2</v>
       </c>
-      <c r="R49" s="26">
+      <c r="R49" s="20">
         <f t="shared" si="4"/>
         <v>-4.3312426408462279E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:18">
+    <row r="50" spans="1:18" ht="17">
       <c r="A50" s="12" t="s">
         <v>789</v>
       </c>
@@ -6112,20 +6157,20 @@
       <c r="O50" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="P50" s="26">
+      <c r="P50" s="20">
         <f t="shared" si="0"/>
         <v>-9.6995690269249688E-2</v>
       </c>
-      <c r="Q50" s="26">
+      <c r="Q50" s="20">
         <f t="shared" si="3"/>
         <v>-0.10903930281288467</v>
       </c>
-      <c r="R50" s="26">
+      <c r="R50" s="20">
         <f t="shared" si="4"/>
         <v>-8.433660168235102E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:18" ht="17">
       <c r="A51" s="12" t="s">
         <v>671</v>
       </c>
@@ -6171,20 +6216,20 @@
       <c r="O51" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="P51" s="26">
+      <c r="P51" s="20">
         <f t="shared" si="0"/>
         <v>-0.14859254745743056</v>
       </c>
-      <c r="Q51" s="26">
+      <c r="Q51" s="20">
         <f t="shared" si="3"/>
         <v>-0.14845716986350585</v>
       </c>
-      <c r="R51" s="26">
+      <c r="R51" s="20">
         <f t="shared" si="4"/>
         <v>-9.997549652265289E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:18">
+    <row r="52" spans="1:18" ht="17">
       <c r="A52" s="12" t="s">
         <v>675</v>
       </c>
@@ -6230,20 +6275,20 @@
       <c r="O52" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="P52" s="26">
+      <c r="P52" s="20">
         <f t="shared" si="0"/>
         <v>-9.5558135059241201E-3</v>
       </c>
-      <c r="Q52" s="26">
+      <c r="Q52" s="20">
         <f t="shared" si="3"/>
         <v>-5.6065118597007487E-3</v>
       </c>
-      <c r="R52" s="26">
+      <c r="R52" s="20">
         <f t="shared" si="4"/>
         <v>-3.4605739662588188E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:18">
+    <row r="53" spans="1:18" ht="17">
       <c r="A53" s="12" t="s">
         <v>678</v>
       </c>
@@ -6289,20 +6334,20 @@
       <c r="O53" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="P53" s="26">
+      <c r="P53" s="20">
         <f t="shared" si="0"/>
         <v>-1.8452297999296385E-2</v>
       </c>
-      <c r="Q53" s="26">
+      <c r="Q53" s="20">
         <f t="shared" si="3"/>
         <v>-2.2929891365636199E-2</v>
       </c>
-      <c r="R53" s="26">
+      <c r="R53" s="20">
         <f t="shared" si="4"/>
         <v>-1.8781473224341528E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
+    <row r="54" spans="1:18" ht="17">
       <c r="A54" s="12" t="s">
         <v>679</v>
       </c>
@@ -6348,20 +6393,20 @@
       <c r="O54" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="P54" s="26">
+      <c r="P54" s="20">
         <f t="shared" si="0"/>
         <v>-4.4720353235455826E-2</v>
       </c>
-      <c r="Q54" s="26">
+      <c r="Q54" s="20">
         <f t="shared" si="3"/>
         <v>-3.1560462888827133E-3</v>
       </c>
-      <c r="R54" s="26">
+      <c r="R54" s="20">
         <f t="shared" si="4"/>
         <v>-3.3639890691314907E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:18" ht="17">
       <c r="A55" s="12" t="s">
         <v>682</v>
       </c>
@@ -6407,20 +6452,20 @@
       <c r="O55" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="P55" s="26">
+      <c r="P55" s="20">
         <f t="shared" si="0"/>
         <v>-1.9436082225775083E-2</v>
       </c>
-      <c r="Q55" s="26">
+      <c r="Q55" s="20">
         <f t="shared" si="3"/>
         <v>2.9144120755507062E-2</v>
       </c>
-      <c r="R55" s="26">
+      <c r="R55" s="20">
         <f t="shared" si="4"/>
         <v>-3.4155714131469685E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:18">
+    <row r="56" spans="1:18" ht="17">
       <c r="A56" s="12" t="s">
         <v>683</v>
       </c>
@@ -6466,20 +6511,20 @@
       <c r="O56" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="P56" s="26">
+      <c r="P56" s="20">
         <f t="shared" si="0"/>
         <v>3.6456099256716216E-2</v>
       </c>
-      <c r="Q56" s="26">
+      <c r="Q56" s="20">
         <f t="shared" si="3"/>
         <v>6.1149072107444594E-2</v>
       </c>
-      <c r="R56" s="26">
+      <c r="R56" s="20">
         <f t="shared" si="4"/>
         <v>3.0286296037125269E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:18">
+    <row r="57" spans="1:18" ht="17">
       <c r="A57" s="12" t="s">
         <v>684</v>
       </c>
@@ -6525,20 +6570,20 @@
       <c r="O57" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="P57" s="26">
+      <c r="P57" s="20">
         <f t="shared" si="0"/>
         <v>7.7614232607740863E-2</v>
       </c>
-      <c r="Q57" s="26">
+      <c r="Q57" s="20">
         <f t="shared" si="3"/>
         <v>0.13171922886041645</v>
       </c>
-      <c r="R57" s="26">
+      <c r="R57" s="20">
         <f t="shared" si="4"/>
         <v>7.2901416419514989E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
+    <row r="58" spans="1:18" ht="17">
       <c r="A58" s="12" t="s">
         <v>686</v>
       </c>
@@ -6584,20 +6629,20 @@
       <c r="O58" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="P58" s="26">
+      <c r="P58" s="20">
         <f t="shared" si="0"/>
         <v>0.12591976144357619</v>
       </c>
-      <c r="Q58" s="26">
+      <c r="Q58" s="20">
         <f t="shared" si="3"/>
         <v>0.17813263931078807</v>
       </c>
-      <c r="R58" s="26">
+      <c r="R58" s="20">
         <f t="shared" si="4"/>
         <v>7.8249596491886356E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:18">
+    <row r="59" spans="1:18" ht="17">
       <c r="A59" s="12" t="s">
         <v>688</v>
       </c>
@@ -6643,20 +6688,20 @@
       <c r="O59" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="P59" s="26">
+      <c r="P59" s="20">
         <f t="shared" si="0"/>
         <v>-4.9601500538836434E-2</v>
       </c>
-      <c r="Q59" s="26">
+      <c r="Q59" s="20">
         <f t="shared" si="3"/>
         <v>-1.8220978587068712E-2</v>
       </c>
-      <c r="R59" s="26">
+      <c r="R59" s="20">
         <f t="shared" si="4"/>
         <v>-1.8234038319420859E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:18">
+    <row r="60" spans="1:18" ht="17">
       <c r="A60" s="12" t="s">
         <v>690</v>
       </c>
@@ -6702,20 +6747,20 @@
       <c r="O60" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="P60" s="26">
+      <c r="P60" s="20">
         <f t="shared" si="0"/>
         <v>-3.0912699317267686E-2</v>
       </c>
-      <c r="Q60" s="26">
+      <c r="Q60" s="20">
         <f t="shared" si="3"/>
         <v>-7.7956244947965953E-3</v>
       </c>
-      <c r="R60" s="26">
+      <c r="R60" s="20">
         <f t="shared" si="4"/>
         <v>-1.2615536737715089E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:18">
+    <row r="61" spans="1:18" ht="17">
       <c r="A61" s="12" t="s">
         <v>692</v>
       </c>
@@ -6761,20 +6806,20 @@
       <c r="O61" s="15" t="s">
         <v>627</v>
       </c>
-      <c r="P61" s="26">
+      <c r="P61" s="20">
         <f t="shared" si="0"/>
         <v>2.2767514201405045E-2</v>
       </c>
-      <c r="Q61" s="26">
+      <c r="Q61" s="20">
         <f t="shared" si="3"/>
         <v>1.6541236013928914E-2</v>
       </c>
-      <c r="R61" s="26">
+      <c r="R61" s="20">
         <f t="shared" si="4"/>
         <v>9.3879431367735518E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:18">
+    <row r="62" spans="1:18" ht="17">
       <c r="A62" s="12" t="s">
         <v>694</v>
       </c>
@@ -6820,20 +6865,20 @@
       <c r="O62" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="P62" s="26">
+      <c r="P62" s="20">
         <f t="shared" si="0"/>
         <v>3.5338537993833165E-2</v>
       </c>
-      <c r="Q62" s="26">
+      <c r="Q62" s="20">
         <f t="shared" si="3"/>
         <v>2.2201560570410193E-2</v>
       </c>
-      <c r="R62" s="26">
+      <c r="R62" s="20">
         <f t="shared" si="4"/>
         <v>1.1363029182459253E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:18">
+    <row r="63" spans="1:18" ht="17">
       <c r="A63" s="12" t="s">
         <v>695</v>
       </c>
@@ -6879,20 +6924,20 @@
       <c r="O63" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="P63" s="26">
+      <c r="P63" s="20">
         <f t="shared" si="0"/>
         <v>-3.3238753206076893E-3</v>
       </c>
-      <c r="Q63" s="26">
+      <c r="Q63" s="20">
         <f t="shared" si="3"/>
         <v>-1.5139542497418905E-2</v>
       </c>
-      <c r="R63" s="26">
+      <c r="R63" s="20">
         <f t="shared" si="4"/>
         <v>-2.0010160902201805E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:18" ht="17">
       <c r="A64" s="12" t="s">
         <v>696</v>
       </c>
@@ -6938,20 +6983,20 @@
       <c r="O64" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="P64" s="26">
+      <c r="P64" s="20">
         <f t="shared" si="0"/>
         <v>1.7665529049483597E-2</v>
       </c>
-      <c r="Q64" s="26">
+      <c r="Q64" s="20">
         <f t="shared" si="3"/>
         <v>-1.0410332785455136E-2</v>
       </c>
-      <c r="R64" s="26">
+      <c r="R64" s="20">
         <f t="shared" si="4"/>
         <v>-1.0883661748307238E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:18">
+    <row r="65" spans="1:18" ht="17">
       <c r="A65" s="12" t="s">
         <v>698</v>
       </c>
@@ -6997,20 +7042,20 @@
       <c r="O65" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="P65" s="26">
+      <c r="P65" s="20">
         <f t="shared" si="0"/>
         <v>2.0357613940068305E-2</v>
       </c>
-      <c r="Q65" s="26">
+      <c r="Q65" s="20">
         <f t="shared" si="3"/>
         <v>-1.6942348196634763E-2</v>
       </c>
-      <c r="R65" s="26">
+      <c r="R65" s="20">
         <f t="shared" si="4"/>
         <v>-1.3500160372571516E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
+    <row r="66" spans="1:18" ht="17">
       <c r="A66" s="12" t="s">
         <v>700</v>
       </c>
@@ -7056,20 +7101,20 @@
       <c r="O66" s="16" t="s">
         <v>474</v>
       </c>
-      <c r="P66" s="26">
+      <c r="P66" s="20">
         <f t="shared" si="0"/>
         <v>2.8000523959470204E-2</v>
       </c>
-      <c r="Q66" s="26">
+      <c r="Q66" s="20">
         <f t="shared" si="3"/>
         <v>-2.2895948814334766E-2</v>
       </c>
-      <c r="R66" s="26">
+      <c r="R66" s="20">
         <f t="shared" si="4"/>
         <v>-3.0532482184527577E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:18">
+    <row r="67" spans="1:18" ht="17">
       <c r="A67" s="12" t="s">
         <v>701</v>
       </c>
@@ -7115,20 +7160,20 @@
       <c r="O67" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="P67" s="26">
+      <c r="P67" s="20">
         <f t="shared" si="0"/>
         <v>3.2630070069454419E-2</v>
       </c>
-      <c r="Q67" s="26">
+      <c r="Q67" s="20">
         <f t="shared" si="3"/>
         <v>5.9265916292157461E-4</v>
       </c>
-      <c r="R67" s="26">
+      <c r="R67" s="20">
         <f t="shared" si="4"/>
         <v>-1.3147295929838748E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
+    <row r="68" spans="1:18" ht="17">
       <c r="A68" s="12" t="s">
         <v>705</v>
       </c>
@@ -7174,20 +7219,20 @@
       <c r="O68" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="P68" s="26">
+      <c r="P68" s="20">
         <f t="shared" si="0"/>
         <v>0.13307773686729202</v>
       </c>
-      <c r="Q68" s="26">
+      <c r="Q68" s="20">
         <f t="shared" si="3"/>
         <v>0.14093404840441731</v>
       </c>
-      <c r="R68" s="26">
+      <c r="R68" s="20">
         <f t="shared" si="4"/>
         <v>0.14378102190481998</v>
       </c>
     </row>
-    <row r="69" spans="1:18">
+    <row r="69" spans="1:18" ht="17">
       <c r="A69" s="12" t="s">
         <v>707</v>
       </c>
@@ -7233,20 +7278,20 @@
       <c r="O69" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="P69" s="26">
+      <c r="P69" s="20">
         <f t="shared" si="0"/>
         <v>0.33668179592671615</v>
       </c>
-      <c r="Q69" s="26">
+      <c r="Q69" s="20">
         <f t="shared" si="3"/>
         <v>8.383433446538166E-2</v>
       </c>
-      <c r="R69" s="26">
+      <c r="R69" s="20">
         <f t="shared" si="4"/>
         <v>9.7194835940788663E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:18">
+    <row r="70" spans="1:18" ht="17">
       <c r="A70" s="12" t="s">
         <v>710</v>
       </c>
@@ -7292,20 +7337,20 @@
       <c r="O70" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="P70" s="26">
+      <c r="P70" s="20">
         <f t="shared" si="0"/>
         <v>1.6619869529544955E-2</v>
       </c>
-      <c r="Q70" s="26">
+      <c r="Q70" s="20">
         <f t="shared" si="3"/>
         <v>9.0083416478642625E-2</v>
       </c>
-      <c r="R70" s="26">
+      <c r="R70" s="20">
         <f t="shared" si="4"/>
         <v>9.7135711370859815E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:18">
+    <row r="71" spans="1:18" ht="17">
       <c r="A71" s="12" t="s">
         <v>712</v>
       </c>
@@ -7351,20 +7396,20 @@
       <c r="O71" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="P71" s="26">
+      <c r="P71" s="20">
         <f t="shared" si="0"/>
         <v>0.22029778730966074</v>
       </c>
-      <c r="Q71" s="26">
+      <c r="Q71" s="20">
         <f t="shared" si="3"/>
         <v>7.2671083813880891E-2</v>
       </c>
-      <c r="R71" s="26">
+      <c r="R71" s="20">
         <f t="shared" si="4"/>
         <v>7.4028027934533322E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:18">
+    <row r="72" spans="1:18" ht="17">
       <c r="A72" s="12" t="s">
         <v>713</v>
       </c>
@@ -7410,20 +7455,20 @@
       <c r="O72" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="P72" s="26">
+      <c r="P72" s="20">
         <f t="shared" ref="P72:P135" si="5">(B72-B65)/B65</f>
         <v>-2.578297036081909E-5</v>
       </c>
-      <c r="Q72" s="26">
+      <c r="Q72" s="20">
         <f t="shared" si="3"/>
         <v>9.6010101685433252E-2</v>
       </c>
-      <c r="R72" s="26">
+      <c r="R72" s="20">
         <f t="shared" si="4"/>
         <v>9.2005409975750269E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:18">
+    <row r="73" spans="1:18" ht="17">
       <c r="A73" s="12" t="s">
         <v>714</v>
       </c>
@@ -7469,20 +7514,20 @@
       <c r="O73" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="P73" s="26">
+      <c r="P73" s="20">
         <f t="shared" si="5"/>
         <v>6.1141834107693784E-2</v>
       </c>
-      <c r="Q73" s="26">
+      <c r="Q73" s="20">
         <f t="shared" si="3"/>
         <v>8.2936513753968752E-2</v>
       </c>
-      <c r="R73" s="26">
+      <c r="R73" s="20">
         <f t="shared" si="4"/>
         <v>0.1117249477411439</v>
       </c>
     </row>
-    <row r="74" spans="1:18">
+    <row r="74" spans="1:18" ht="17">
       <c r="A74" s="12" t="s">
         <v>715</v>
       </c>
@@ -7528,20 +7573,20 @@
       <c r="O74" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="P74" s="26">
+      <c r="P74" s="20">
         <f t="shared" si="5"/>
         <v>-0.32608392012863169</v>
       </c>
-      <c r="Q74" s="26">
+      <c r="Q74" s="20">
         <f t="shared" si="3"/>
         <v>4.7650259111819762E-2</v>
       </c>
-      <c r="R74" s="26">
+      <c r="R74" s="20">
         <f t="shared" si="4"/>
         <v>7.1222295280048059E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
+    <row r="75" spans="1:18" ht="17">
       <c r="A75" s="12" t="s">
         <v>719</v>
       </c>
@@ -7587,20 +7632,20 @@
       <c r="O75" s="15" t="s">
         <v>722</v>
       </c>
-      <c r="P75" s="26">
+      <c r="P75" s="20">
         <f t="shared" si="5"/>
         <v>-0.12433558257645902</v>
       </c>
-      <c r="Q75" s="26">
+      <c r="Q75" s="20">
         <f t="shared" si="3"/>
         <v>-8.0545658321523425E-2</v>
       </c>
-      <c r="R75" s="26">
+      <c r="R75" s="20">
         <f t="shared" si="4"/>
         <v>-7.8816912985699858E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
+    <row r="76" spans="1:18" ht="17">
       <c r="A76" s="12" t="s">
         <v>723</v>
       </c>
@@ -7646,20 +7691,20 @@
       <c r="O76" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="P76" s="26">
+      <c r="P76" s="20">
         <f t="shared" si="5"/>
         <v>-6.368081718400527E-2</v>
       </c>
-      <c r="Q76" s="26">
+      <c r="Q76" s="20">
         <f t="shared" si="3"/>
         <v>-5.8857926519193839E-2</v>
       </c>
-      <c r="R76" s="26">
+      <c r="R76" s="20">
         <f t="shared" si="4"/>
         <v>-5.6260742563250483E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
+    <row r="77" spans="1:18" ht="17">
       <c r="A77" s="12" t="s">
         <v>725</v>
       </c>
@@ -7705,20 +7750,20 @@
       <c r="O77" s="15" t="s">
         <v>491</v>
       </c>
-      <c r="P77" s="26">
+      <c r="P77" s="20">
         <f t="shared" si="5"/>
         <v>2.6602106553963011E-2</v>
       </c>
-      <c r="Q77" s="26">
+      <c r="Q77" s="20">
         <f t="shared" si="3"/>
         <v>-1.2227733804943625E-2</v>
       </c>
-      <c r="R77" s="26">
+      <c r="R77" s="20">
         <f t="shared" si="4"/>
         <v>-5.8508578567196606E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
+    <row r="78" spans="1:18" ht="17">
       <c r="A78" s="12" t="s">
         <v>727</v>
       </c>
@@ -7764,20 +7809,20 @@
       <c r="O78" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="P78" s="26">
+      <c r="P78" s="20">
         <f t="shared" si="5"/>
         <v>3.0114431558800118E-2</v>
       </c>
-      <c r="Q78" s="26">
+      <c r="Q78" s="20">
         <f t="shared" ref="Q78:Q141" si="6">(E78-E71)/E71</f>
         <v>-1.1104267254594917E-2</v>
       </c>
-      <c r="R78" s="26">
+      <c r="R78" s="20">
         <f t="shared" ref="R78:R141" si="7">(F78-F71)/F71</f>
         <v>-4.4088129251221011E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:18">
+    <row r="79" spans="1:18" ht="17">
       <c r="A79" s="12" t="s">
         <v>728</v>
       </c>
@@ -7823,20 +7868,20 @@
       <c r="O79" s="16" t="s">
         <v>581</v>
       </c>
-      <c r="P79" s="26">
+      <c r="P79" s="20">
         <f t="shared" si="5"/>
         <v>0.16501085168020652</v>
       </c>
-      <c r="Q79" s="26">
+      <c r="Q79" s="20">
         <f t="shared" si="6"/>
         <v>-6.7123867645279223E-2</v>
       </c>
-      <c r="R79" s="26">
+      <c r="R79" s="20">
         <f t="shared" si="7"/>
         <v>-5.2544105822421808E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:18" ht="17">
       <c r="A80" s="12" t="s">
         <v>732</v>
       </c>
@@ -7882,20 +7927,20 @@
       <c r="O80" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="P80" s="26">
+      <c r="P80" s="20">
         <f t="shared" si="5"/>
         <v>3.626845334361882E-2</v>
       </c>
-      <c r="Q80" s="26">
+      <c r="Q80" s="20">
         <f t="shared" si="6"/>
         <v>-1.4824743663635823E-2</v>
       </c>
-      <c r="R80" s="26">
+      <c r="R80" s="20">
         <f t="shared" si="7"/>
         <v>-1.672309263492722E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:18">
+    <row r="81" spans="1:18" ht="17">
       <c r="A81" s="12" t="s">
         <v>734</v>
       </c>
@@ -7941,20 +7986,20 @@
       <c r="O81" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="P81" s="26">
+      <c r="P81" s="20">
         <f t="shared" si="5"/>
         <v>-1.1354170759484609E-2</v>
       </c>
-      <c r="Q81" s="26">
+      <c r="Q81" s="20">
         <f t="shared" si="6"/>
         <v>-1.9716313495196224E-2</v>
       </c>
-      <c r="R81" s="26">
+      <c r="R81" s="20">
         <f t="shared" si="7"/>
         <v>-2.0180261168792894E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18">
+    <row r="82" spans="1:18" ht="17">
       <c r="A82" s="12" t="s">
         <v>584</v>
       </c>
@@ -8000,20 +8045,20 @@
       <c r="O82" s="15" t="s">
         <v>588</v>
       </c>
-      <c r="P82" s="26">
+      <c r="P82" s="20">
         <f t="shared" si="5"/>
         <v>2.7027962015787617E-2</v>
       </c>
-      <c r="Q82" s="26">
+      <c r="Q82" s="20">
         <f t="shared" si="6"/>
         <v>-8.5044624593905195E-3</v>
       </c>
-      <c r="R82" s="26">
+      <c r="R82" s="20">
         <f t="shared" si="7"/>
         <v>-8.1146810512444881E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:18">
+    <row r="83" spans="1:18" ht="17">
       <c r="A83" s="12" t="s">
         <v>589</v>
       </c>
@@ -8059,20 +8104,20 @@
       <c r="O83" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="P83" s="26">
+      <c r="P83" s="20">
         <f t="shared" si="5"/>
         <v>3.9767674159572546E-2</v>
       </c>
-      <c r="Q83" s="26">
+      <c r="Q83" s="20">
         <f t="shared" si="6"/>
         <v>4.6571182744544254E-3</v>
       </c>
-      <c r="R83" s="26">
+      <c r="R83" s="20">
         <f t="shared" si="7"/>
         <v>7.3721021165696898E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:18">
+    <row r="84" spans="1:18" ht="17">
       <c r="A84" s="12" t="s">
         <v>591</v>
       </c>
@@ -8118,20 +8163,20 @@
       <c r="O84" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="P84" s="26">
+      <c r="P84" s="20">
         <f t="shared" si="5"/>
         <v>-3.537605321314987E-2</v>
       </c>
-      <c r="Q84" s="26">
+      <c r="Q84" s="20">
         <f t="shared" si="6"/>
         <v>-2.3066582838641322E-2</v>
       </c>
-      <c r="R84" s="26">
+      <c r="R84" s="20">
         <f t="shared" si="7"/>
         <v>-3.0369032757696E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:18" ht="17">
       <c r="A85" s="12" t="s">
         <v>593</v>
       </c>
@@ -8177,20 +8222,20 @@
       <c r="O85" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="P85" s="26">
+      <c r="P85" s="20">
         <f t="shared" si="5"/>
         <v>-1.8616034921062723E-2</v>
       </c>
-      <c r="Q85" s="26">
+      <c r="Q85" s="20">
         <f t="shared" si="6"/>
         <v>-2.4865538064250483E-2</v>
       </c>
-      <c r="R85" s="26">
+      <c r="R85" s="20">
         <f t="shared" si="7"/>
         <v>-2.7407149646049414E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:18">
+    <row r="86" spans="1:18" ht="17">
       <c r="A86" s="12" t="s">
         <v>594</v>
       </c>
@@ -8236,20 +8281,20 @@
       <c r="O86" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="P86" s="26">
+      <c r="P86" s="20">
         <f t="shared" si="5"/>
         <v>-0.13096506727594176</v>
       </c>
-      <c r="Q86" s="26">
+      <c r="Q86" s="20">
         <f t="shared" si="6"/>
         <v>4.9295718641625318E-2</v>
       </c>
-      <c r="R86" s="26">
+      <c r="R86" s="20">
         <f t="shared" si="7"/>
         <v>-1.6616554526908509E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:18">
+    <row r="87" spans="1:18" ht="17">
       <c r="A87" s="12" t="s">
         <v>595</v>
       </c>
@@ -8295,20 +8340,20 @@
       <c r="O87" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="P87" s="26">
+      <c r="P87" s="20">
         <f t="shared" si="5"/>
         <v>-2.6278521934017668E-2</v>
       </c>
-      <c r="Q87" s="26">
+      <c r="Q87" s="20">
         <f t="shared" si="6"/>
         <v>1.6477509669169398E-2</v>
       </c>
-      <c r="R87" s="26">
+      <c r="R87" s="20">
         <f t="shared" si="7"/>
         <v>1.7111318350069477E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:18" ht="17">
       <c r="A88" s="12" t="s">
         <v>596</v>
       </c>
@@ -8354,20 +8399,20 @@
       <c r="O88" s="15" t="s">
         <v>600</v>
       </c>
-      <c r="P88" s="26">
+      <c r="P88" s="20">
         <f t="shared" si="5"/>
         <v>1.5752220978641839E-2</v>
       </c>
-      <c r="Q88" s="26">
+      <c r="Q88" s="20">
         <f t="shared" si="6"/>
         <v>2.9657016146712626E-2</v>
       </c>
-      <c r="R88" s="26">
+      <c r="R88" s="20">
         <f t="shared" si="7"/>
         <v>2.5069731309953238E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:18" ht="17">
       <c r="A89" s="12" t="s">
         <v>601</v>
       </c>
@@ -8413,20 +8458,20 @@
       <c r="O89" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="P89" s="26">
+      <c r="P89" s="20">
         <f t="shared" si="5"/>
         <v>5.151312669500549E-2</v>
       </c>
-      <c r="Q89" s="26">
+      <c r="Q89" s="20">
         <f t="shared" si="6"/>
         <v>1.0892350424338301E-2</v>
       </c>
-      <c r="R89" s="26">
+      <c r="R89" s="20">
         <f t="shared" si="7"/>
         <v>5.2899429516857083E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:18">
+    <row r="90" spans="1:18" ht="17">
       <c r="A90" s="12" t="s">
         <v>606</v>
       </c>
@@ -8472,20 +8517,20 @@
       <c r="O90" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="P90" s="26">
+      <c r="P90" s="20">
         <f t="shared" si="5"/>
         <v>6.6119594525389541E-2</v>
       </c>
-      <c r="Q90" s="26">
+      <c r="Q90" s="20">
         <f t="shared" si="6"/>
         <v>3.880049852852565E-2</v>
       </c>
-      <c r="R90" s="26">
+      <c r="R90" s="20">
         <f t="shared" si="7"/>
         <v>9.7250149670375062E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:18" ht="17">
       <c r="A91" s="12" t="s">
         <v>610</v>
       </c>
@@ -8531,20 +8576,20 @@
       <c r="O91" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="P91" s="26">
+      <c r="P91" s="20">
         <f t="shared" si="5"/>
         <v>7.5600209221232159E-2</v>
       </c>
-      <c r="Q91" s="26">
+      <c r="Q91" s="20">
         <f t="shared" si="6"/>
         <v>4.1368260586923798E-2</v>
       </c>
-      <c r="R91" s="26">
+      <c r="R91" s="20">
         <f t="shared" si="7"/>
         <v>1.4051492883881132E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:18">
+    <row r="92" spans="1:18" ht="17">
       <c r="A92" s="12" t="s">
         <v>614</v>
       </c>
@@ -8590,20 +8635,20 @@
       <c r="O92" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="P92" s="26">
+      <c r="P92" s="20">
         <f t="shared" si="5"/>
         <v>9.8770276844724503E-2</v>
       </c>
-      <c r="Q92" s="26">
+      <c r="Q92" s="20">
         <f t="shared" si="6"/>
         <v>7.4947286047249206E-2</v>
       </c>
-      <c r="R92" s="26">
+      <c r="R92" s="20">
         <f t="shared" si="7"/>
         <v>5.3208304853041698E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:18">
+    <row r="93" spans="1:18" ht="17">
       <c r="A93" s="12" t="s">
         <v>615</v>
       </c>
@@ -8649,20 +8694,20 @@
       <c r="O93" s="16" t="s">
         <v>616</v>
       </c>
-      <c r="P93" s="26">
+      <c r="P93" s="20">
         <f t="shared" si="5"/>
         <v>4.9921918788097021E-2</v>
       </c>
-      <c r="Q93" s="26">
+      <c r="Q93" s="20">
         <f t="shared" si="6"/>
         <v>2.6786297768732068E-2</v>
       </c>
-      <c r="R93" s="26">
+      <c r="R93" s="20">
         <f t="shared" si="7"/>
         <v>1.3646012099069838E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:18">
+    <row r="94" spans="1:18" ht="17">
       <c r="A94" s="12" t="s">
         <v>617</v>
       </c>
@@ -8708,20 +8753,20 @@
       <c r="O94" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="P94" s="26">
+      <c r="P94" s="20">
         <f t="shared" si="5"/>
         <v>-1.1192151706492679E-2</v>
       </c>
-      <c r="Q94" s="26">
+      <c r="Q94" s="20">
         <f t="shared" si="6"/>
         <v>-3.9965000080904541E-2</v>
       </c>
-      <c r="R94" s="26">
+      <c r="R94" s="20">
         <f t="shared" si="7"/>
         <v>-4.2839607042440241E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:18">
+    <row r="95" spans="1:18" ht="17">
       <c r="A95" s="12" t="s">
         <v>619</v>
       </c>
@@ -8767,20 +8812,20 @@
       <c r="O95" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="P95" s="26">
+      <c r="P95" s="20">
         <f t="shared" si="5"/>
         <v>3.7355027441529784E-2</v>
       </c>
-      <c r="Q95" s="26">
+      <c r="Q95" s="20">
         <f t="shared" si="6"/>
         <v>-6.0841184587853096E-3</v>
       </c>
-      <c r="R95" s="26">
+      <c r="R95" s="20">
         <f t="shared" si="7"/>
         <v>-1.5157536205726421E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:18">
+    <row r="96" spans="1:18" ht="17">
       <c r="A96" s="12" t="s">
         <v>620</v>
       </c>
@@ -8826,20 +8871,20 @@
       <c r="O96" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="P96" s="26">
+      <c r="P96" s="20">
         <f t="shared" si="5"/>
         <v>9.1711676925177649E-2</v>
       </c>
-      <c r="Q96" s="26">
+      <c r="Q96" s="20">
         <f t="shared" si="6"/>
         <v>4.5415477157332004E-2</v>
       </c>
-      <c r="R96" s="26">
+      <c r="R96" s="20">
         <f t="shared" si="7"/>
         <v>6.2997657223348061E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:18" ht="17">
       <c r="A97" s="12" t="s">
         <v>626</v>
       </c>
@@ -8885,20 +8930,20 @@
       <c r="O97" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="P97" s="26">
+      <c r="P97" s="20">
         <f t="shared" si="5"/>
         <v>5.300912530375488E-2</v>
       </c>
-      <c r="Q97" s="26">
+      <c r="Q97" s="20">
         <f t="shared" si="6"/>
         <v>2.7481606032402003E-2</v>
       </c>
-      <c r="R97" s="26">
+      <c r="R97" s="20">
         <f t="shared" si="7"/>
         <v>9.4077526518805354E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:18" ht="17">
       <c r="A98" s="12" t="s">
         <v>629</v>
       </c>
@@ -8944,20 +8989,20 @@
       <c r="O98" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="P98" s="26">
+      <c r="P98" s="20">
         <f t="shared" si="5"/>
         <v>0.16881690783125422</v>
       </c>
-      <c r="Q98" s="26">
+      <c r="Q98" s="20">
         <f t="shared" si="6"/>
         <v>-3.2132257938159971E-2</v>
       </c>
-      <c r="R98" s="26">
+      <c r="R98" s="20">
         <f t="shared" si="7"/>
         <v>1.3626285126639274E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:18" ht="17">
       <c r="A99" s="12" t="s">
         <v>630</v>
       </c>
@@ -9003,20 +9048,20 @@
       <c r="O99" s="16" t="s">
         <v>634</v>
       </c>
-      <c r="P99" s="26">
+      <c r="P99" s="20">
         <f t="shared" si="5"/>
         <v>-9.9297699104046108E-2</v>
       </c>
-      <c r="Q99" s="26">
+      <c r="Q99" s="20">
         <f t="shared" si="6"/>
         <v>-0.19172002248066791</v>
       </c>
-      <c r="R99" s="26">
+      <c r="R99" s="20">
         <f t="shared" si="7"/>
         <v>-0.12797187196359727</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:18" ht="17">
       <c r="A100" s="12" t="s">
         <v>635</v>
       </c>
@@ -9062,20 +9107,20 @@
       <c r="O100" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="P100" s="26">
+      <c r="P100" s="20">
         <f t="shared" si="5"/>
         <v>6.9465704927813177E-2</v>
       </c>
-      <c r="Q100" s="26">
+      <c r="Q100" s="20">
         <f t="shared" si="6"/>
         <v>-0.22736094040161153</v>
       </c>
-      <c r="R100" s="26">
+      <c r="R100" s="20">
         <f t="shared" si="7"/>
         <v>-0.13602719180104264</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:18" ht="17">
       <c r="A101" s="12" t="s">
         <v>638</v>
       </c>
@@ -9121,20 +9166,20 @@
       <c r="O101" s="16" t="s">
         <v>642</v>
       </c>
-      <c r="P101" s="26">
+      <c r="P101" s="20">
         <f t="shared" si="5"/>
         <v>-7.7334673653360997E-2</v>
       </c>
-      <c r="Q101" s="26">
+      <c r="Q101" s="20">
         <f t="shared" si="6"/>
         <v>-0.12600614954505657</v>
       </c>
-      <c r="R101" s="26">
+      <c r="R101" s="20">
         <f t="shared" si="7"/>
         <v>-0.11876103958720637</v>
       </c>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:18" ht="17">
       <c r="A102" s="12" t="s">
         <v>643</v>
       </c>
@@ -9180,20 +9225,20 @@
       <c r="O102" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="P102" s="26">
+      <c r="P102" s="20">
         <f t="shared" si="5"/>
         <v>-0.1482354355934071</v>
       </c>
-      <c r="Q102" s="26">
+      <c r="Q102" s="20">
         <f t="shared" si="6"/>
         <v>-0.31211148580018688</v>
       </c>
-      <c r="R102" s="26">
+      <c r="R102" s="20">
         <f t="shared" si="7"/>
         <v>-0.28211936428288376</v>
       </c>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:18" ht="17">
       <c r="A103" s="12" t="s">
         <v>646</v>
       </c>
@@ -9239,20 +9284,20 @@
       <c r="O103" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="P103" s="26">
+      <c r="P103" s="20">
         <f t="shared" si="5"/>
         <v>-0.48135167717745048</v>
       </c>
-      <c r="Q103" s="26">
+      <c r="Q103" s="20">
         <f t="shared" si="6"/>
         <v>-0.49975579367330641</v>
       </c>
-      <c r="R103" s="26">
+      <c r="R103" s="20">
         <f t="shared" si="7"/>
         <v>-0.41027740073375607</v>
       </c>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:18" ht="17">
       <c r="A104" s="12" t="s">
         <v>648</v>
       </c>
@@ -9298,20 +9343,20 @@
       <c r="O104" s="15" t="s">
         <v>534</v>
       </c>
-      <c r="P104" s="26">
+      <c r="P104" s="20">
         <f t="shared" si="5"/>
         <v>-0.6201658946825932</v>
       </c>
-      <c r="Q104" s="26">
+      <c r="Q104" s="20">
         <f t="shared" si="6"/>
         <v>-0.4315263192698357</v>
       </c>
-      <c r="R104" s="26">
+      <c r="R104" s="20">
         <f t="shared" si="7"/>
         <v>-0.36259483278076715</v>
       </c>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:18" ht="17">
       <c r="A105" s="12" t="s">
         <v>650</v>
       </c>
@@ -9357,20 +9402,20 @@
       <c r="O105" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="P105" s="26">
+      <c r="P105" s="20">
         <f t="shared" si="5"/>
         <v>-0.38477884741266177</v>
       </c>
-      <c r="Q105" s="26">
+      <c r="Q105" s="20">
         <f t="shared" si="6"/>
         <v>-0.33472082576135181</v>
       </c>
-      <c r="R105" s="26">
+      <c r="R105" s="20">
         <f t="shared" si="7"/>
         <v>-0.24575010558708144</v>
       </c>
     </row>
-    <row r="106" spans="1:18">
+    <row r="106" spans="1:18" ht="17">
       <c r="A106" s="12" t="s">
         <v>653</v>
       </c>
@@ -9416,20 +9461,20 @@
       <c r="O106" s="15" t="s">
         <v>656</v>
       </c>
-      <c r="P106" s="26">
+      <c r="P106" s="20">
         <f t="shared" si="5"/>
         <v>-0.12674445352203631</v>
       </c>
-      <c r="Q106" s="26">
+      <c r="Q106" s="20">
         <f t="shared" si="6"/>
         <v>-0.10405783468415035</v>
       </c>
-      <c r="R106" s="26">
+      <c r="R106" s="20">
         <f t="shared" si="7"/>
         <v>-4.4246915224708645E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:18">
+    <row r="107" spans="1:18" ht="17">
       <c r="A107" s="12" t="s">
         <v>657</v>
       </c>
@@ -9475,20 +9520,20 @@
       <c r="O107" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="P107" s="26">
+      <c r="P107" s="20">
         <f t="shared" si="5"/>
         <v>0.30563752432972457</v>
       </c>
-      <c r="Q107" s="26">
+      <c r="Q107" s="20">
         <f t="shared" si="6"/>
         <v>0.27522132141714495</v>
       </c>
-      <c r="R107" s="26">
+      <c r="R107" s="20">
         <f t="shared" si="7"/>
         <v>0.19275243321359578</v>
       </c>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:18" ht="17">
       <c r="A108" s="12" t="s">
         <v>661</v>
       </c>
@@ -9534,20 +9579,20 @@
       <c r="O108" s="16" t="s">
         <v>664</v>
       </c>
-      <c r="P108" s="26">
+      <c r="P108" s="20">
         <f t="shared" si="5"/>
         <v>0.24798883322442178</v>
       </c>
-      <c r="Q108" s="26">
+      <c r="Q108" s="20">
         <f t="shared" si="6"/>
         <v>0.20689416957581269</v>
       </c>
-      <c r="R108" s="26">
+      <c r="R108" s="20">
         <f t="shared" si="7"/>
         <v>0.19501003831856026</v>
       </c>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:18" ht="17">
       <c r="A109" s="12" t="s">
         <v>665</v>
       </c>
@@ -9593,20 +9638,20 @@
       <c r="O109" s="15" t="s">
         <v>571</v>
       </c>
-      <c r="P109" s="26">
+      <c r="P109" s="20">
         <f t="shared" si="5"/>
         <v>0.51369353907554127</v>
       </c>
-      <c r="Q109" s="26">
+      <c r="Q109" s="20">
         <f t="shared" si="6"/>
         <v>0.46223469929596034</v>
       </c>
-      <c r="R109" s="26">
+      <c r="R109" s="20">
         <f t="shared" si="7"/>
         <v>0.40663066772463946</v>
       </c>
     </row>
-    <row r="110" spans="1:18">
+    <row r="110" spans="1:18" ht="17">
       <c r="A110" s="12" t="s">
         <v>666</v>
       </c>
@@ -9652,20 +9697,20 @@
       <c r="O110" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="P110" s="26">
+      <c r="P110" s="20">
         <f t="shared" si="5"/>
         <v>1.0498773751824388</v>
       </c>
-      <c r="Q110" s="26">
+      <c r="Q110" s="20">
         <f t="shared" si="6"/>
         <v>0.96760136233390892</v>
       </c>
-      <c r="R110" s="26">
+      <c r="R110" s="20">
         <f t="shared" si="7"/>
         <v>0.60432808083400347</v>
       </c>
     </row>
-    <row r="111" spans="1:18">
+    <row r="111" spans="1:18" ht="17">
       <c r="A111" s="12" t="s">
         <v>670</v>
       </c>
@@ -9711,20 +9756,20 @@
       <c r="O111" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="P111" s="26">
+      <c r="P111" s="20">
         <f t="shared" si="5"/>
         <v>0.73906125633182895</v>
       </c>
-      <c r="Q111" s="26">
+      <c r="Q111" s="20">
         <f t="shared" si="6"/>
         <v>0.67854517021395877</v>
       </c>
-      <c r="R111" s="26">
+      <c r="R111" s="20">
         <f t="shared" si="7"/>
         <v>0.42043938079116122</v>
       </c>
     </row>
-    <row r="112" spans="1:18">
+    <row r="112" spans="1:18" ht="17">
       <c r="A112" s="12" t="s">
         <v>503</v>
       </c>
@@ -9770,20 +9815,20 @@
       <c r="O112" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="P112" s="26">
+      <c r="P112" s="20">
         <f t="shared" si="5"/>
         <v>0.55964969172956258</v>
       </c>
-      <c r="Q112" s="26">
+      <c r="Q112" s="20">
         <f t="shared" si="6"/>
         <v>0.51033287780308834</v>
       </c>
-      <c r="R112" s="26">
+      <c r="R112" s="20">
         <f t="shared" si="7"/>
         <v>0.29850038037479659</v>
       </c>
     </row>
-    <row r="113" spans="1:18">
+    <row r="113" spans="1:18" ht="17">
       <c r="A113" s="12" t="s">
         <v>506</v>
       </c>
@@ -9829,20 +9874,20 @@
       <c r="O113" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="P113" s="26">
+      <c r="P113" s="20">
         <f t="shared" si="5"/>
         <v>0.33608045128817871</v>
       </c>
-      <c r="Q113" s="26">
+      <c r="Q113" s="20">
         <f t="shared" si="6"/>
         <v>0.33606995331735834</v>
       </c>
-      <c r="R113" s="26">
+      <c r="R113" s="20">
         <f t="shared" si="7"/>
         <v>0.16221080793346837</v>
       </c>
     </row>
-    <row r="114" spans="1:18">
+    <row r="114" spans="1:18" ht="17">
       <c r="A114" s="12" t="s">
         <v>507</v>
       </c>
@@ -9888,20 +9933,20 @@
       <c r="O114" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="P114" s="26">
+      <c r="P114" s="20">
         <f t="shared" si="5"/>
         <v>-8.7183155271085985E-2</v>
       </c>
-      <c r="Q114" s="26">
+      <c r="Q114" s="20">
         <f t="shared" si="6"/>
         <v>-3.45578945247942E-2</v>
       </c>
-      <c r="R114" s="26">
+      <c r="R114" s="20">
         <f t="shared" si="7"/>
         <v>-6.9731360021291419E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:18">
+    <row r="115" spans="1:18" ht="17">
       <c r="A115" s="12" t="s">
         <v>510</v>
       </c>
@@ -9947,20 +9992,20 @@
       <c r="O115" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="P115" s="26">
+      <c r="P115" s="20">
         <f t="shared" si="5"/>
         <v>-0.10622526747458146</v>
       </c>
-      <c r="Q115" s="26">
+      <c r="Q115" s="20">
         <f t="shared" si="6"/>
         <v>-6.9132249675270693E-2</v>
       </c>
-      <c r="R115" s="26">
+      <c r="R115" s="20">
         <f t="shared" si="7"/>
         <v>-6.2908470880925507E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:18">
+    <row r="116" spans="1:18" ht="17">
       <c r="A116" s="12" t="s">
         <v>515</v>
       </c>
@@ -10006,20 +10051,20 @@
       <c r="O116" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="P116" s="26">
+      <c r="P116" s="20">
         <f t="shared" si="5"/>
         <v>-9.1655194232335452E-2</v>
       </c>
-      <c r="Q116" s="26">
+      <c r="Q116" s="20">
         <f t="shared" si="6"/>
         <v>-5.4102511425364881E-2</v>
       </c>
-      <c r="R116" s="26">
+      <c r="R116" s="20">
         <f t="shared" si="7"/>
         <v>-4.3109297054079516E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:18">
+    <row r="117" spans="1:18" ht="17">
       <c r="A117" s="12" t="s">
         <v>518</v>
       </c>
@@ -10065,20 +10110,20 @@
       <c r="O117" s="15" t="s">
         <v>521</v>
       </c>
-      <c r="P117" s="26">
+      <c r="P117" s="20">
         <f t="shared" si="5"/>
         <v>-4.8070658138053009E-2</v>
       </c>
-      <c r="Q117" s="26">
+      <c r="Q117" s="20">
         <f t="shared" si="6"/>
         <v>-2.2051272041303176E-2</v>
       </c>
-      <c r="R117" s="26">
+      <c r="R117" s="20">
         <f t="shared" si="7"/>
         <v>-9.2803992550777141E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:18">
+    <row r="118" spans="1:18" ht="17">
       <c r="A118" s="12" t="s">
         <v>522</v>
       </c>
@@ -10124,20 +10169,20 @@
       <c r="O118" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="P118" s="26">
+      <c r="P118" s="20">
         <f t="shared" si="5"/>
         <v>-4.8833681814451753E-2</v>
       </c>
-      <c r="Q118" s="26">
+      <c r="Q118" s="20">
         <f t="shared" si="6"/>
         <v>-2.5478646041390329E-2</v>
       </c>
-      <c r="R118" s="26">
+      <c r="R118" s="20">
         <f t="shared" si="7"/>
         <v>-1.5934947814597724E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:18">
+    <row r="119" spans="1:18" ht="17">
       <c r="A119" s="12" t="s">
         <v>526</v>
       </c>
@@ -10183,20 +10228,20 @@
       <c r="O119" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="P119" s="26">
+      <c r="P119" s="20">
         <f t="shared" si="5"/>
         <v>-8.2748663887124721E-2</v>
       </c>
-      <c r="Q119" s="26">
+      <c r="Q119" s="20">
         <f t="shared" si="6"/>
         <v>-3.4776340804486439E-2</v>
       </c>
-      <c r="R119" s="26">
+      <c r="R119" s="20">
         <f t="shared" si="7"/>
         <v>-4.1911287438082021E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:18">
+    <row r="120" spans="1:18" ht="17">
       <c r="A120" s="12" t="s">
         <v>527</v>
       </c>
@@ -10242,20 +10287,20 @@
       <c r="O120" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="P120" s="26">
+      <c r="P120" s="20">
         <f t="shared" si="5"/>
         <v>-8.8071806091625807E-2</v>
       </c>
-      <c r="Q120" s="26">
+      <c r="Q120" s="20">
         <f t="shared" si="6"/>
         <v>-6.3746084110079163E-2</v>
       </c>
-      <c r="R120" s="26">
+      <c r="R120" s="20">
         <f t="shared" si="7"/>
         <v>-6.250065430513746E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:18">
+    <row r="121" spans="1:18" ht="17">
       <c r="A121" s="12" t="s">
         <v>528</v>
       </c>
@@ -10301,20 +10346,20 @@
       <c r="O121" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="P121" s="26">
+      <c r="P121" s="20">
         <f t="shared" si="5"/>
         <v>-2.214910295376479E-2</v>
       </c>
-      <c r="Q121" s="26">
+      <c r="Q121" s="20">
         <f t="shared" si="6"/>
         <v>-1.8154816717054559E-2</v>
       </c>
-      <c r="R121" s="26">
+      <c r="R121" s="20">
         <f t="shared" si="7"/>
         <v>-1.713076765217492E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:18">
+    <row r="122" spans="1:18" ht="17">
       <c r="A122" s="12" t="s">
         <v>531</v>
       </c>
@@ -10360,20 +10405,20 @@
       <c r="O122" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="P122" s="26">
+      <c r="P122" s="20">
         <f t="shared" si="5"/>
         <v>-2.7325343051628238E-2</v>
       </c>
-      <c r="Q122" s="26">
+      <c r="Q122" s="20">
         <f t="shared" si="6"/>
         <v>-1.3557292843609309E-2</v>
       </c>
-      <c r="R122" s="26">
+      <c r="R122" s="20">
         <f t="shared" si="7"/>
         <v>-1.1026771374260747E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:18">
+    <row r="123" spans="1:18" ht="17">
       <c r="A123" s="12" t="s">
         <v>533</v>
       </c>
@@ -10419,20 +10464,20 @@
       <c r="O123" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="P123" s="26">
+      <c r="P123" s="20">
         <f t="shared" si="5"/>
         <v>3.6626830437292673E-2</v>
       </c>
-      <c r="Q123" s="26">
+      <c r="Q123" s="20">
         <f t="shared" si="6"/>
         <v>2.017573934054636E-2</v>
       </c>
-      <c r="R123" s="26">
+      <c r="R123" s="20">
         <f t="shared" si="7"/>
         <v>9.8902857085815168E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:18">
+    <row r="124" spans="1:18" ht="17">
       <c r="A124" s="12" t="s">
         <v>536</v>
       </c>
@@ -10478,20 +10523,20 @@
       <c r="O124" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="P124" s="26">
+      <c r="P124" s="20">
         <f t="shared" si="5"/>
         <v>2.0460175395803901E-2</v>
       </c>
-      <c r="Q124" s="26">
+      <c r="Q124" s="20">
         <f t="shared" si="6"/>
         <v>3.357474461344042E-2</v>
       </c>
-      <c r="R124" s="26">
+      <c r="R124" s="20">
         <f t="shared" si="7"/>
         <v>1.5748988624940456E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:18">
+    <row r="125" spans="1:18" ht="17">
       <c r="A125" s="12" t="s">
         <v>541</v>
       </c>
@@ -10537,20 +10582,20 @@
       <c r="O125" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="P125" s="26">
+      <c r="P125" s="20">
         <f t="shared" si="5"/>
         <v>-1.6982257041404367E-2</v>
       </c>
-      <c r="Q125" s="26">
+      <c r="Q125" s="20">
         <f t="shared" si="6"/>
         <v>2.5514886804243592E-2</v>
       </c>
-      <c r="R125" s="26">
+      <c r="R125" s="20">
         <f t="shared" si="7"/>
         <v>-7.9568187142934378E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:18">
+    <row r="126" spans="1:18" ht="17">
       <c r="A126" s="12" t="s">
         <v>543</v>
       </c>
@@ -10596,20 +10641,20 @@
       <c r="O126" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="P126" s="26">
+      <c r="P126" s="20">
         <f t="shared" si="5"/>
         <v>8.4781026161646292E-3</v>
       </c>
-      <c r="Q126" s="26">
+      <c r="Q126" s="20">
         <f t="shared" si="6"/>
         <v>1.3369709400478999E-2</v>
       </c>
-      <c r="R126" s="26">
+      <c r="R126" s="20">
         <f t="shared" si="7"/>
         <v>-7.5179965875899341E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:18">
+    <row r="127" spans="1:18" ht="17">
       <c r="A127" s="12" t="s">
         <v>545</v>
       </c>
@@ -10655,20 +10700,20 @@
       <c r="O127" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="P127" s="26">
+      <c r="P127" s="20">
         <f t="shared" si="5"/>
         <v>4.9984584559433706E-3</v>
       </c>
-      <c r="Q127" s="26">
+      <c r="Q127" s="20">
         <f t="shared" si="6"/>
         <v>1.3381755061529004E-2</v>
       </c>
-      <c r="R127" s="26">
+      <c r="R127" s="20">
         <f t="shared" si="7"/>
         <v>3.048286832852568E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:18">
+    <row r="128" spans="1:18" ht="17">
       <c r="A128" s="12" t="s">
         <v>546</v>
       </c>
@@ -10714,20 +10759,20 @@
       <c r="O128" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="P128" s="26">
+      <c r="P128" s="20">
         <f t="shared" si="5"/>
         <v>-1.3245663520046623E-2</v>
       </c>
-      <c r="Q128" s="26">
+      <c r="Q128" s="20">
         <f t="shared" si="6"/>
         <v>-4.7051389141603436E-2</v>
       </c>
-      <c r="R128" s="26">
+      <c r="R128" s="20">
         <f t="shared" si="7"/>
         <v>-4.5096837292603033E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:18">
+    <row r="129" spans="1:18" ht="17">
       <c r="A129" s="12" t="s">
         <v>551</v>
       </c>
@@ -10773,20 +10818,20 @@
       <c r="O129" s="15" t="s">
         <v>552</v>
       </c>
-      <c r="P129" s="26">
+      <c r="P129" s="20">
         <f t="shared" si="5"/>
         <v>0.27634278495854669</v>
       </c>
-      <c r="Q129" s="26">
+      <c r="Q129" s="20">
         <f t="shared" si="6"/>
         <v>0.18305941177442359</v>
       </c>
-      <c r="R129" s="26">
+      <c r="R129" s="20">
         <f t="shared" si="7"/>
         <v>0.15178518677519789</v>
       </c>
     </row>
-    <row r="130" spans="1:18">
+    <row r="130" spans="1:18" ht="17">
       <c r="A130" s="12" t="s">
         <v>553</v>
       </c>
@@ -10832,20 +10877,20 @@
       <c r="O130" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="P130" s="26">
+      <c r="P130" s="20">
         <f t="shared" si="5"/>
         <v>0.37512160068696626</v>
       </c>
-      <c r="Q130" s="26">
+      <c r="Q130" s="20">
         <f t="shared" si="6"/>
         <v>0.1277716581481422</v>
       </c>
-      <c r="R130" s="26">
+      <c r="R130" s="20">
         <f t="shared" si="7"/>
         <v>0.11712682607388451</v>
       </c>
     </row>
-    <row r="131" spans="1:18">
+    <row r="131" spans="1:18" ht="17">
       <c r="A131" s="12" t="s">
         <v>556</v>
       </c>
@@ -10891,20 +10936,20 @@
       <c r="O131" s="15" t="s">
         <v>559</v>
       </c>
-      <c r="P131" s="26">
+      <c r="P131" s="20">
         <f t="shared" si="5"/>
         <v>3.194037769293816E-3</v>
       </c>
-      <c r="Q131" s="26">
+      <c r="Q131" s="20">
         <f t="shared" si="6"/>
         <v>8.3109438084767992E-2</v>
       </c>
-      <c r="R131" s="26">
+      <c r="R131" s="20">
         <f t="shared" si="7"/>
         <v>8.4280443937562621E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:18">
+    <row r="132" spans="1:18" ht="17">
       <c r="A132" s="12" t="s">
         <v>560</v>
       </c>
@@ -10950,20 +10995,20 @@
       <c r="O132" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="P132" s="26">
+      <c r="P132" s="20">
         <f t="shared" si="5"/>
         <v>0.28343853740379021</v>
       </c>
-      <c r="Q132" s="26">
+      <c r="Q132" s="20">
         <f t="shared" si="6"/>
         <v>8.0869002051280392E-2</v>
       </c>
-      <c r="R132" s="26">
+      <c r="R132" s="20">
         <f t="shared" si="7"/>
         <v>9.4479495192732896E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:18">
+    <row r="133" spans="1:18" ht="17">
       <c r="A133" s="12" t="s">
         <v>563</v>
       </c>
@@ -11009,20 +11054,20 @@
       <c r="O133" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="P133" s="26">
+      <c r="P133" s="20">
         <f t="shared" si="5"/>
         <v>4.5357743919676868E-2</v>
       </c>
-      <c r="Q133" s="26">
+      <c r="Q133" s="20">
         <f t="shared" si="6"/>
         <v>0.10377572368764475</v>
       </c>
-      <c r="R133" s="26">
+      <c r="R133" s="20">
         <f t="shared" si="7"/>
         <v>0.11906701391961018</v>
       </c>
     </row>
-    <row r="134" spans="1:18">
+    <row r="134" spans="1:18" ht="17">
       <c r="A134" s="12" t="s">
         <v>564</v>
       </c>
@@ -11068,20 +11113,20 @@
       <c r="O134" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="P134" s="26">
+      <c r="P134" s="20">
         <f t="shared" si="5"/>
         <v>-3.8384711687633999E-3</v>
       </c>
-      <c r="Q134" s="26">
+      <c r="Q134" s="20">
         <f t="shared" si="6"/>
         <v>0.10760597844799286</v>
       </c>
-      <c r="R134" s="26">
+      <c r="R134" s="20">
         <f t="shared" si="7"/>
         <v>0.11429874120028126</v>
       </c>
     </row>
-    <row r="135" spans="1:18">
+    <row r="135" spans="1:18" ht="17">
       <c r="A135" s="12" t="s">
         <v>566</v>
       </c>
@@ -11127,20 +11172,20 @@
       <c r="O135" s="16" t="s">
         <v>418</v>
       </c>
-      <c r="P135" s="26">
+      <c r="P135" s="20">
         <f t="shared" si="5"/>
         <v>-0.3891242382764824</v>
       </c>
-      <c r="Q135" s="26">
+      <c r="Q135" s="20">
         <f t="shared" si="6"/>
         <v>0.1520706309850246</v>
       </c>
-      <c r="R135" s="26">
+      <c r="R135" s="20">
         <f t="shared" si="7"/>
         <v>0.13295609082450224</v>
       </c>
     </row>
-    <row r="136" spans="1:18">
+    <row r="136" spans="1:18" ht="17">
       <c r="A136" s="12" t="s">
         <v>567</v>
       </c>
@@ -11186,20 +11231,20 @@
       <c r="O136" s="16" t="s">
         <v>496</v>
       </c>
-      <c r="P136" s="26">
+      <c r="P136" s="20">
         <f t="shared" ref="P136:P199" si="8">(B136-B129)/B129</f>
         <v>-0.16770782377341439</v>
       </c>
-      <c r="Q136" s="26">
+      <c r="Q136" s="20">
         <f t="shared" si="6"/>
         <v>-5.0292859748117716E-2</v>
       </c>
-      <c r="R136" s="26">
+      <c r="R136" s="20">
         <f t="shared" si="7"/>
         <v>-5.2333588606976629E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:18">
+    <row r="137" spans="1:18" ht="17">
       <c r="A137" s="12" t="s">
         <v>569</v>
       </c>
@@ -11245,20 +11290,20 @@
       <c r="O137" s="15" t="s">
         <v>572</v>
       </c>
-      <c r="P137" s="26">
+      <c r="P137" s="20">
         <f t="shared" si="8"/>
         <v>-0.12018581428140443</v>
       </c>
-      <c r="Q137" s="26">
+      <c r="Q137" s="20">
         <f t="shared" si="6"/>
         <v>-6.0488093696884522E-2</v>
       </c>
-      <c r="R137" s="26">
+      <c r="R137" s="20">
         <f t="shared" si="7"/>
         <v>-4.8652182622342E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:18">
+    <row r="138" spans="1:18" ht="17">
       <c r="A138" s="12" t="s">
         <v>573</v>
       </c>
@@ -11304,20 +11349,20 @@
       <c r="O138" s="15" t="s">
         <v>575</v>
       </c>
-      <c r="P138" s="26">
+      <c r="P138" s="20">
         <f t="shared" si="8"/>
         <v>-4.2505889402160754E-2</v>
       </c>
-      <c r="Q138" s="26">
+      <c r="Q138" s="20">
         <f t="shared" si="6"/>
         <v>1.6198037081648346E-2</v>
       </c>
-      <c r="R138" s="26">
+      <c r="R138" s="20">
         <f t="shared" si="7"/>
         <v>6.4769795780332037E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:18">
+    <row r="139" spans="1:18" ht="17">
       <c r="A139" s="12" t="s">
         <v>576</v>
       </c>
@@ -11363,20 +11408,20 @@
       <c r="O139" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="P139" s="26">
+      <c r="P139" s="20">
         <f t="shared" si="8"/>
         <v>-7.0597485768080864E-2</v>
       </c>
-      <c r="Q139" s="26">
+      <c r="Q139" s="20">
         <f t="shared" si="6"/>
         <v>-2.6821416979029053E-2</v>
       </c>
-      <c r="R139" s="26">
+      <c r="R139" s="20">
         <f t="shared" si="7"/>
         <v>-3.4374973382235038E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:18">
+    <row r="140" spans="1:18" ht="17">
       <c r="A140" s="12" t="s">
         <v>579</v>
       </c>
@@ -11422,20 +11467,20 @@
       <c r="O140" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="P140" s="26">
+      <c r="P140" s="20">
         <f t="shared" si="8"/>
         <v>-5.178976756229401E-2</v>
       </c>
-      <c r="Q140" s="26">
+      <c r="Q140" s="20">
         <f t="shared" si="6"/>
         <v>-9.5007689513677968E-3</v>
       </c>
-      <c r="R140" s="26">
+      <c r="R140" s="20">
         <f t="shared" si="7"/>
         <v>-2.0950939342629107E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:18">
+    <row r="141" spans="1:18" ht="17">
       <c r="A141" s="12" t="s">
         <v>580</v>
       </c>
@@ -11481,20 +11526,20 @@
       <c r="O141" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="P141" s="26">
+      <c r="P141" s="20">
         <f t="shared" si="8"/>
         <v>-4.9058890744542963E-2</v>
       </c>
-      <c r="Q141" s="26">
+      <c r="Q141" s="20">
         <f t="shared" si="6"/>
         <v>-3.0898298066268308E-2</v>
       </c>
-      <c r="R141" s="26">
+      <c r="R141" s="20">
         <f t="shared" si="7"/>
         <v>-3.0339725635474154E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:18">
+    <row r="142" spans="1:18" ht="17">
       <c r="A142" s="12" t="s">
         <v>582</v>
       </c>
@@ -11540,20 +11585,20 @@
       <c r="O142" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="P142" s="26">
+      <c r="P142" s="20">
         <f t="shared" si="8"/>
         <v>-4.6330326559852433E-2</v>
       </c>
-      <c r="Q142" s="26">
+      <c r="Q142" s="20">
         <f t="shared" ref="Q142:Q205" si="9">(E142-E135)/E135</f>
         <v>-4.0339187169169968E-2</v>
       </c>
-      <c r="R142" s="26">
+      <c r="R142" s="20">
         <f t="shared" ref="R142:R205" si="10">(F142-F135)/F135</f>
         <v>-2.3993298941104857E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:18">
+    <row r="143" spans="1:18" ht="17">
       <c r="A143" s="12" t="s">
         <v>409</v>
       </c>
@@ -11599,20 +11644,20 @@
       <c r="O143" s="16" t="s">
         <v>413</v>
       </c>
-      <c r="P143" s="26">
+      <c r="P143" s="20">
         <f t="shared" si="8"/>
         <v>-2.22897232789828E-2</v>
       </c>
-      <c r="Q143" s="26">
+      <c r="Q143" s="20">
         <f t="shared" si="9"/>
         <v>-2.467516376592422E-2</v>
       </c>
-      <c r="R143" s="26">
+      <c r="R143" s="20">
         <f t="shared" si="10"/>
         <v>-3.5408975296677327E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:18">
+    <row r="144" spans="1:18" ht="17">
       <c r="A144" s="12" t="s">
         <v>414</v>
       </c>
@@ -11658,20 +11703,20 @@
       <c r="O144" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="P144" s="26">
+      <c r="P144" s="20">
         <f t="shared" si="8"/>
         <v>1.2372522987491518E-2</v>
       </c>
-      <c r="Q144" s="26">
+      <c r="Q144" s="20">
         <f t="shared" si="9"/>
         <v>4.8578557386965071E-3</v>
       </c>
-      <c r="R144" s="26">
+      <c r="R144" s="20">
         <f t="shared" si="10"/>
         <v>5.5951582517539608E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:18">
+    <row r="145" spans="1:18" ht="17">
       <c r="A145" s="12" t="s">
         <v>417</v>
       </c>
@@ -11717,20 +11762,20 @@
       <c r="O145" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="P145" s="26">
+      <c r="P145" s="20">
         <f t="shared" si="8"/>
         <v>-5.5558848026828547E-2</v>
       </c>
-      <c r="Q145" s="26">
+      <c r="Q145" s="20">
         <f t="shared" si="9"/>
         <v>-6.1868496985227915E-2</v>
       </c>
-      <c r="R145" s="26">
+      <c r="R145" s="20">
         <f t="shared" si="10"/>
         <v>-4.7208187889274715E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:18">
+    <row r="146" spans="1:18" ht="17">
       <c r="A146" s="12" t="s">
         <v>421</v>
       </c>
@@ -11776,20 +11821,20 @@
       <c r="O146" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="P146" s="26">
+      <c r="P146" s="20">
         <f t="shared" si="8"/>
         <v>4.6785035458902148E-2</v>
       </c>
-      <c r="Q146" s="26">
+      <c r="Q146" s="20">
         <f t="shared" si="9"/>
         <v>4.1396723734450053E-2</v>
       </c>
-      <c r="R146" s="26">
+      <c r="R146" s="20">
         <f t="shared" si="10"/>
         <v>3.1196820132286404E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:18">
+    <row r="147" spans="1:18" ht="17">
       <c r="A147" s="12" t="s">
         <v>425</v>
       </c>
@@ -11835,20 +11880,20 @@
       <c r="O147" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="P147" s="26">
+      <c r="P147" s="20">
         <f t="shared" si="8"/>
         <v>2.8499327058356602E-3</v>
       </c>
-      <c r="Q147" s="26">
+      <c r="Q147" s="20">
         <f t="shared" si="9"/>
         <v>1.1433409633540578E-2</v>
       </c>
-      <c r="R147" s="26">
+      <c r="R147" s="20">
         <f t="shared" si="10"/>
         <v>-2.7973394033711085E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:18">
+    <row r="148" spans="1:18" ht="17">
       <c r="A148" s="12" t="s">
         <v>427</v>
       </c>
@@ -11894,20 +11939,20 @@
       <c r="O148" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="P148" s="26">
+      <c r="P148" s="20">
         <f t="shared" si="8"/>
         <v>4.3870923330526078E-2</v>
       </c>
-      <c r="Q148" s="26">
+      <c r="Q148" s="20">
         <f t="shared" si="9"/>
         <v>5.3774290341870042E-2</v>
       </c>
-      <c r="R148" s="26">
+      <c r="R148" s="20">
         <f t="shared" si="10"/>
         <v>2.6871385420357302E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:18">
+    <row r="149" spans="1:18" ht="17">
       <c r="A149" s="12" t="s">
         <v>429</v>
       </c>
@@ -11953,20 +11998,20 @@
       <c r="O149" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="P149" s="26">
+      <c r="P149" s="20">
         <f t="shared" si="8"/>
         <v>1.4013561187192901E-2</v>
       </c>
-      <c r="Q149" s="26">
+      <c r="Q149" s="20">
         <f t="shared" si="9"/>
         <v>3.2450899231944594E-2</v>
       </c>
-      <c r="R149" s="26">
+      <c r="R149" s="20">
         <f t="shared" si="10"/>
         <v>1.2261865689088372E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:18">
+    <row r="150" spans="1:18" ht="17">
       <c r="A150" s="12" t="s">
         <v>434</v>
       </c>
@@ -12012,20 +12057,20 @@
       <c r="O150" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="P150" s="26">
+      <c r="P150" s="20">
         <f t="shared" si="8"/>
         <v>-2.643581728550146E-2</v>
       </c>
-      <c r="Q150" s="26">
+      <c r="Q150" s="20">
         <f t="shared" si="9"/>
         <v>-2.0226680814703399E-2</v>
       </c>
-      <c r="R150" s="26">
+      <c r="R150" s="20">
         <f t="shared" si="10"/>
         <v>-1.5825242373925567E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:18">
+    <row r="151" spans="1:18" ht="17">
       <c r="A151" s="12" t="s">
         <v>438</v>
       </c>
@@ -12071,20 +12116,20 @@
       <c r="O151" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="P151" s="26">
+      <c r="P151" s="20">
         <f t="shared" si="8"/>
         <v>-3.0598982642121967E-2</v>
       </c>
-      <c r="Q151" s="26">
+      <c r="Q151" s="20">
         <f t="shared" si="9"/>
         <v>-2.0639378491751473E-2</v>
       </c>
-      <c r="R151" s="26">
+      <c r="R151" s="20">
         <f t="shared" si="10"/>
         <v>-1.6008169924145593E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:18">
+    <row r="152" spans="1:18" ht="17">
       <c r="A152" s="12" t="s">
         <v>441</v>
       </c>
@@ -12130,20 +12175,20 @@
       <c r="O152" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="P152" s="26">
+      <c r="P152" s="20">
         <f t="shared" si="8"/>
         <v>-3.0687496466921833E-2</v>
       </c>
-      <c r="Q152" s="26">
+      <c r="Q152" s="20">
         <f t="shared" si="9"/>
         <v>-2.459073989567314E-2</v>
       </c>
-      <c r="R152" s="26">
+      <c r="R152" s="20">
         <f t="shared" si="10"/>
         <v>-4.7181978106071609E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:18">
+    <row r="153" spans="1:18" ht="17">
       <c r="A153" s="12" t="s">
         <v>444</v>
       </c>
@@ -12189,20 +12234,20 @@
       <c r="O153" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="P153" s="26">
+      <c r="P153" s="20">
         <f t="shared" si="8"/>
         <v>-5.3798839527798761E-3</v>
       </c>
-      <c r="Q153" s="26">
+      <c r="Q153" s="20">
         <f t="shared" si="9"/>
         <v>-3.4070345923546951E-4</v>
       </c>
-      <c r="R153" s="26">
+      <c r="R153" s="20">
         <f t="shared" si="10"/>
         <v>8.020403369240578E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:18">
+    <row r="154" spans="1:18" ht="17">
       <c r="A154" s="12" t="s">
         <v>446</v>
       </c>
@@ -12248,20 +12293,20 @@
       <c r="O154" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="P154" s="26">
+      <c r="P154" s="20">
         <f t="shared" si="8"/>
         <v>-8.5501187677428543E-3</v>
       </c>
-      <c r="Q154" s="26">
+      <c r="Q154" s="20">
         <f t="shared" si="9"/>
         <v>-1.8723019936954056E-2</v>
       </c>
-      <c r="R154" s="26">
+      <c r="R154" s="20">
         <f t="shared" si="10"/>
         <v>-6.3934997308142984E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:18">
+    <row r="155" spans="1:18" ht="17">
       <c r="A155" s="12" t="s">
         <v>448</v>
       </c>
@@ -12307,20 +12352,20 @@
       <c r="O155" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="P155" s="26">
+      <c r="P155" s="20">
         <f t="shared" si="8"/>
         <v>-3.0294573861535498E-3</v>
       </c>
-      <c r="Q155" s="26">
+      <c r="Q155" s="20">
         <f t="shared" si="9"/>
         <v>-7.2969427708391293E-3</v>
       </c>
-      <c r="R155" s="26">
+      <c r="R155" s="20">
         <f t="shared" si="10"/>
         <v>-1.1746288023388132E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:18">
+    <row r="156" spans="1:18" ht="17">
       <c r="A156" s="12" t="s">
         <v>451</v>
       </c>
@@ -12366,20 +12411,20 @@
       <c r="O156" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="P156" s="26">
+      <c r="P156" s="20">
         <f t="shared" si="8"/>
         <v>7.3434294611755033E-2</v>
       </c>
-      <c r="Q156" s="26">
+      <c r="Q156" s="20">
         <f t="shared" si="9"/>
         <v>2.4338607936252674E-2</v>
       </c>
-      <c r="R156" s="26">
+      <c r="R156" s="20">
         <f t="shared" si="10"/>
         <v>2.1346158330944821E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:18">
+    <row r="157" spans="1:18" ht="17">
       <c r="A157" s="12" t="s">
         <v>454</v>
       </c>
@@ -12425,20 +12470,20 @@
       <c r="O157" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="P157" s="26">
+      <c r="P157" s="20">
         <f t="shared" si="8"/>
         <v>4.9164036465162084E-2</v>
       </c>
-      <c r="Q157" s="26">
+      <c r="Q157" s="20">
         <f t="shared" si="9"/>
         <v>5.4447894452325785E-3</v>
       </c>
-      <c r="R157" s="26">
+      <c r="R157" s="20">
         <f t="shared" si="10"/>
         <v>1.0819653216385299E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:18">
+    <row r="158" spans="1:18" ht="17">
       <c r="A158" s="12" t="s">
         <v>459</v>
       </c>
@@ -12484,20 +12529,20 @@
       <c r="O158" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="P158" s="26">
+      <c r="P158" s="20">
         <f t="shared" si="8"/>
         <v>7.7646779745142317E-3</v>
       </c>
-      <c r="Q158" s="26">
+      <c r="Q158" s="20">
         <f t="shared" si="9"/>
         <v>1.3155592399247155E-2</v>
       </c>
-      <c r="R158" s="26">
+      <c r="R158" s="20">
         <f t="shared" si="10"/>
         <v>2.3249250133680902E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:18">
+    <row r="159" spans="1:18" ht="17">
       <c r="A159" s="12" t="s">
         <v>463</v>
       </c>
@@ -12543,20 +12588,20 @@
       <c r="O159" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="P159" s="26">
+      <c r="P159" s="20">
         <f t="shared" si="8"/>
         <v>0.11929849582647829</v>
       </c>
-      <c r="Q159" s="26">
+      <c r="Q159" s="20">
         <f t="shared" si="9"/>
         <v>8.0092171263246192E-2</v>
       </c>
-      <c r="R159" s="26">
+      <c r="R159" s="20">
         <f t="shared" si="10"/>
         <v>8.5491483442413613E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:18">
+    <row r="160" spans="1:18" ht="17">
       <c r="A160" s="12" t="s">
         <v>466</v>
       </c>
@@ -12602,20 +12647,20 @@
       <c r="O160" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="P160" s="26">
+      <c r="P160" s="20">
         <f t="shared" si="8"/>
         <v>2.0572396769347131E-2</v>
       </c>
-      <c r="Q160" s="26">
+      <c r="Q160" s="20">
         <f t="shared" si="9"/>
         <v>2.121685899332787E-2</v>
       </c>
-      <c r="R160" s="26">
+      <c r="R160" s="20">
         <f t="shared" si="10"/>
         <v>-4.2281954839773761E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:18">
+    <row r="161" spans="1:18" ht="17">
       <c r="A161" s="12" t="s">
         <v>468</v>
       </c>
@@ -12661,20 +12706,20 @@
       <c r="O161" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="P161" s="26">
+      <c r="P161" s="20">
         <f t="shared" si="8"/>
         <v>0.26435527159275068</v>
       </c>
-      <c r="Q161" s="26">
+      <c r="Q161" s="20">
         <f t="shared" si="9"/>
         <v>7.9519658460411161E-2</v>
       </c>
-      <c r="R161" s="26">
+      <c r="R161" s="20">
         <f t="shared" si="10"/>
         <v>3.8352173125134892E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:18">
+    <row r="162" spans="1:18" ht="17">
       <c r="A162" s="12" t="s">
         <v>471</v>
       </c>
@@ -12720,20 +12765,20 @@
       <c r="O162" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="P162" s="26">
+      <c r="P162" s="20">
         <f t="shared" si="8"/>
         <v>5.6883886723962516E-2</v>
       </c>
-      <c r="Q162" s="26">
+      <c r="Q162" s="20">
         <f t="shared" si="9"/>
         <v>2.2281930002413158E-2</v>
       </c>
-      <c r="R162" s="26">
+      <c r="R162" s="20">
         <f t="shared" si="10"/>
         <v>-8.7335740711981958E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:18">
+    <row r="163" spans="1:18" ht="17">
       <c r="A163" s="12" t="s">
         <v>473</v>
       </c>
@@ -12779,20 +12824,20 @@
       <c r="O163" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P163" s="26">
+      <c r="P163" s="20">
         <f t="shared" si="8"/>
         <v>0.1617781074486743</v>
       </c>
-      <c r="Q163" s="26">
+      <c r="Q163" s="20">
         <f t="shared" si="9"/>
         <v>2.4895211242030508E-3</v>
       </c>
-      <c r="R163" s="26">
+      <c r="R163" s="20">
         <f t="shared" si="10"/>
         <v>-3.6123833220147894E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:18">
+    <row r="164" spans="1:18" ht="17">
       <c r="A164" s="12" t="s">
         <v>475</v>
       </c>
@@ -12838,20 +12883,20 @@
       <c r="O164" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="P164" s="26">
+      <c r="P164" s="20">
         <f t="shared" si="8"/>
         <v>-7.4485111013691666E-2</v>
       </c>
-      <c r="Q164" s="26">
+      <c r="Q164" s="20">
         <f t="shared" si="9"/>
         <v>-3.1285726674046228E-2</v>
       </c>
-      <c r="R164" s="26">
+      <c r="R164" s="20">
         <f t="shared" si="10"/>
         <v>-4.1604963959154168E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:18">
+    <row r="165" spans="1:18" ht="17">
       <c r="A165" s="12" t="s">
         <v>478</v>
       </c>
@@ -12897,20 +12942,20 @@
       <c r="O165" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="P165" s="26">
+      <c r="P165" s="20">
         <f t="shared" si="8"/>
         <v>-0.36509025322410449</v>
       </c>
-      <c r="Q165" s="26">
+      <c r="Q165" s="20">
         <f t="shared" si="9"/>
         <v>-6.7992171184438219E-2</v>
       </c>
-      <c r="R165" s="26">
+      <c r="R165" s="20">
         <f t="shared" si="10"/>
         <v>-8.9782986281662883E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:18">
+    <row r="166" spans="1:18" ht="17">
       <c r="A166" s="12" t="s">
         <v>482</v>
       </c>
@@ -12956,20 +13001,20 @@
       <c r="O166" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="P166" s="26">
+      <c r="P166" s="20">
         <f t="shared" si="8"/>
         <v>-0.15939124151800096</v>
       </c>
-      <c r="Q166" s="26">
+      <c r="Q166" s="20">
         <f t="shared" si="9"/>
         <v>-9.6616491014690054E-2</v>
       </c>
-      <c r="R166" s="26">
+      <c r="R166" s="20">
         <f t="shared" si="10"/>
         <v>-0.12261598173535156</v>
       </c>
     </row>
-    <row r="167" spans="1:18">
+    <row r="167" spans="1:18" ht="17">
       <c r="A167" s="12" t="s">
         <v>486</v>
       </c>
@@ -13015,20 +13060,20 @@
       <c r="O167" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="P167" s="26">
+      <c r="P167" s="20">
         <f t="shared" si="8"/>
         <v>-0.11022596064763293</v>
       </c>
-      <c r="Q167" s="26">
+      <c r="Q167" s="20">
         <f t="shared" si="9"/>
         <v>-0.10057620281201507</v>
       </c>
-      <c r="R167" s="26">
+      <c r="R167" s="20">
         <f t="shared" si="10"/>
         <v>-0.11050366861857248</v>
       </c>
     </row>
-    <row r="168" spans="1:18">
+    <row r="168" spans="1:18" ht="17">
       <c r="A168" s="12" t="s">
         <v>487</v>
       </c>
@@ -13074,20 +13119,20 @@
       <c r="O168" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="P168" s="26">
+      <c r="P168" s="20">
         <f t="shared" si="8"/>
         <v>-6.1617905320928305E-2</v>
       </c>
-      <c r="Q168" s="26">
+      <c r="Q168" s="20">
         <f t="shared" si="9"/>
         <v>-8.464829892376384E-2</v>
       </c>
-      <c r="R168" s="26">
+      <c r="R168" s="20">
         <f t="shared" si="10"/>
         <v>-8.3915213036268643E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:18">
+    <row r="169" spans="1:18" ht="17">
       <c r="A169" s="12" t="s">
         <v>492</v>
       </c>
@@ -13133,20 +13178,20 @@
       <c r="O169" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="P169" s="26">
+      <c r="P169" s="20">
         <f t="shared" si="8"/>
         <v>-3.9028242502109858E-2</v>
       </c>
-      <c r="Q169" s="26">
+      <c r="Q169" s="20">
         <f t="shared" si="9"/>
         <v>-5.7146926938537658E-2</v>
       </c>
-      <c r="R169" s="26">
+      <c r="R169" s="20">
         <f t="shared" si="10"/>
         <v>-5.1904278927215192E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:18">
+    <row r="170" spans="1:18" ht="17">
       <c r="A170" s="12" t="s">
         <v>494</v>
       </c>
@@ -13192,20 +13237,20 @@
       <c r="O170" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="P170" s="26">
+      <c r="P170" s="20">
         <f t="shared" si="8"/>
         <v>-2.3970541544633184E-2</v>
       </c>
-      <c r="Q170" s="26">
+      <c r="Q170" s="20">
         <f t="shared" si="9"/>
         <v>-3.1960919410828889E-2</v>
       </c>
-      <c r="R170" s="26">
+      <c r="R170" s="20">
         <f t="shared" si="10"/>
         <v>-3.3721013461863236E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:18">
+    <row r="171" spans="1:18" ht="17">
       <c r="A171" s="12" t="s">
         <v>497</v>
       </c>
@@ -13251,20 +13296,20 @@
       <c r="O171" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="P171" s="26">
+      <c r="P171" s="20">
         <f t="shared" si="8"/>
         <v>-1.3974542295448335E-2</v>
       </c>
-      <c r="Q171" s="26">
+      <c r="Q171" s="20">
         <f t="shared" si="9"/>
         <v>-2.0371152052533537E-2</v>
       </c>
-      <c r="R171" s="26">
+      <c r="R171" s="20">
         <f t="shared" si="10"/>
         <v>-2.0843493411355024E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:18">
+    <row r="172" spans="1:18" ht="17">
       <c r="A172" s="12" t="s">
         <v>500</v>
       </c>
@@ -13310,20 +13355,20 @@
       <c r="O172" s="15" t="s">
         <v>502</v>
       </c>
-      <c r="P172" s="26">
+      <c r="P172" s="20">
         <f t="shared" si="8"/>
         <v>1.5563972200465284E-2</v>
       </c>
-      <c r="Q172" s="26">
+      <c r="Q172" s="20">
         <f t="shared" si="9"/>
         <v>7.3263575159950058E-3</v>
       </c>
-      <c r="R172" s="26">
+      <c r="R172" s="20">
         <f t="shared" si="10"/>
         <v>2.6020437340701212E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:18">
+    <row r="173" spans="1:18" ht="17">
       <c r="A173" s="12" t="s">
         <v>297</v>
       </c>
@@ -13369,20 +13414,20 @@
       <c r="O173" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="P173" s="26">
+      <c r="P173" s="20">
         <f t="shared" si="8"/>
         <v>1.4291300819610546E-2</v>
       </c>
-      <c r="Q173" s="26">
+      <c r="Q173" s="20">
         <f t="shared" si="9"/>
         <v>-7.565335746425453E-3</v>
       </c>
-      <c r="R173" s="26">
+      <c r="R173" s="20">
         <f t="shared" si="10"/>
         <v>-5.1533205595115797E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:18">
+    <row r="174" spans="1:18" ht="17">
       <c r="A174" s="12" t="s">
         <v>302</v>
       </c>
@@ -13428,20 +13473,20 @@
       <c r="O174" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="P174" s="26">
+      <c r="P174" s="20">
         <f t="shared" si="8"/>
         <v>7.4107218683863016E-3</v>
       </c>
-      <c r="Q174" s="26">
+      <c r="Q174" s="20">
         <f t="shared" si="9"/>
         <v>-4.1098918149070308E-3</v>
       </c>
-      <c r="R174" s="26">
+      <c r="R174" s="20">
         <f t="shared" si="10"/>
         <v>8.2148538018878936E-4</v>
       </c>
     </row>
-    <row r="175" spans="1:18">
+    <row r="175" spans="1:18" ht="17">
       <c r="A175" s="12" t="s">
         <v>307</v>
       </c>
@@ -13487,20 +13532,20 @@
       <c r="O175" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="P175" s="26">
+      <c r="P175" s="20">
         <f t="shared" si="8"/>
         <v>-6.8541427115075576E-2</v>
       </c>
-      <c r="Q175" s="26">
+      <c r="Q175" s="20">
         <f t="shared" si="9"/>
         <v>-5.6001693815204534E-2</v>
       </c>
-      <c r="R175" s="26">
+      <c r="R175" s="20">
         <f t="shared" si="10"/>
         <v>-5.2560848498338399E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:18">
+    <row r="176" spans="1:18" ht="17">
       <c r="A176" s="12" t="s">
         <v>311</v>
       </c>
@@ -13546,20 +13591,20 @@
       <c r="O176" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="P176" s="26">
+      <c r="P176" s="20">
         <f t="shared" si="8"/>
         <v>-4.4660094816473608E-2</v>
       </c>
-      <c r="Q176" s="26">
+      <c r="Q176" s="20">
         <f t="shared" si="9"/>
         <v>-5.7796267332724686E-2</v>
       </c>
-      <c r="R176" s="26">
+      <c r="R176" s="20">
         <f t="shared" si="10"/>
         <v>-5.270496689749863E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:18" ht="17">
       <c r="A177" s="12" t="s">
         <v>314</v>
       </c>
@@ -13605,20 +13650,20 @@
       <c r="O177" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="P177" s="26">
+      <c r="P177" s="20">
         <f t="shared" si="8"/>
         <v>-3.0060110469443787E-2</v>
       </c>
-      <c r="Q177" s="26">
+      <c r="Q177" s="20">
         <f t="shared" si="9"/>
         <v>-4.5664774153099504E-2</v>
       </c>
-      <c r="R177" s="26">
+      <c r="R177" s="20">
         <f t="shared" si="10"/>
         <v>-4.5429118838586954E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:18">
+    <row r="178" spans="1:18" ht="17">
       <c r="A178" s="12" t="s">
         <v>318</v>
       </c>
@@ -13664,20 +13709,20 @@
       <c r="O178" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="P178" s="26">
+      <c r="P178" s="20">
         <f t="shared" si="8"/>
         <v>-6.9905420567061899E-3</v>
       </c>
-      <c r="Q178" s="26">
+      <c r="Q178" s="20">
         <f t="shared" si="9"/>
         <v>-5.9734906196287066E-3</v>
       </c>
-      <c r="R178" s="26">
+      <c r="R178" s="20">
         <f t="shared" si="10"/>
         <v>-2.0828984735350845E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:18">
+    <row r="179" spans="1:18" ht="17">
       <c r="A179" s="12" t="s">
         <v>321</v>
       </c>
@@ -13723,20 +13768,20 @@
       <c r="O179" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="P179" s="26">
+      <c r="P179" s="20">
         <f t="shared" si="8"/>
         <v>3.0746293089285301E-3</v>
       </c>
-      <c r="Q179" s="26">
+      <c r="Q179" s="20">
         <f t="shared" si="9"/>
         <v>-2.7646075311374245E-3</v>
       </c>
-      <c r="R179" s="26">
+      <c r="R179" s="20">
         <f t="shared" si="10"/>
         <v>-3.7755020441898428E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:18">
+    <row r="180" spans="1:18" ht="17">
       <c r="A180" s="12" t="s">
         <v>326</v>
       </c>
@@ -13782,20 +13827,20 @@
       <c r="O180" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="P180" s="26">
+      <c r="P180" s="20">
         <f t="shared" si="8"/>
         <v>1.3405177158997063E-2</v>
       </c>
-      <c r="Q180" s="26">
+      <c r="Q180" s="20">
         <f t="shared" si="9"/>
         <v>-6.916839802165879E-3</v>
       </c>
-      <c r="R180" s="26">
+      <c r="R180" s="20">
         <f t="shared" si="10"/>
         <v>9.2352676866176413E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:18">
+    <row r="181" spans="1:18" ht="17">
       <c r="A181" s="12" t="s">
         <v>332</v>
       </c>
@@ -13841,20 +13886,20 @@
       <c r="O181" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="P181" s="26">
+      <c r="P181" s="20">
         <f t="shared" si="8"/>
         <v>1.9823474654124085E-2</v>
       </c>
-      <c r="Q181" s="26">
+      <c r="Q181" s="20">
         <f t="shared" si="9"/>
         <v>1.3566084025649452E-2</v>
       </c>
-      <c r="R181" s="26">
+      <c r="R181" s="20">
         <f t="shared" si="10"/>
         <v>1.6430458473561366E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:18">
+    <row r="182" spans="1:18" ht="17">
       <c r="A182" s="12" t="s">
         <v>335</v>
       </c>
@@ -13900,20 +13945,20 @@
       <c r="O182" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="P182" s="26">
+      <c r="P182" s="20">
         <f t="shared" si="8"/>
         <v>-5.9738939947677976E-2</v>
       </c>
-      <c r="Q182" s="26">
+      <c r="Q182" s="20">
         <f t="shared" si="9"/>
         <v>-7.8512831037500758E-2</v>
       </c>
-      <c r="R182" s="26">
+      <c r="R182" s="20">
         <f t="shared" si="10"/>
         <v>-6.4859880841561204E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:18">
+    <row r="183" spans="1:18" ht="17">
       <c r="A183" s="12" t="s">
         <v>338</v>
       </c>
@@ -13959,20 +14004,20 @@
       <c r="O183" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="P183" s="26">
+      <c r="P183" s="20">
         <f t="shared" si="8"/>
         <v>-0.26489511558230738</v>
       </c>
-      <c r="Q183" s="26">
+      <c r="Q183" s="20">
         <f t="shared" si="9"/>
         <v>-0.23731914812755189</v>
       </c>
-      <c r="R183" s="26">
+      <c r="R183" s="20">
         <f t="shared" si="10"/>
         <v>-8.8027231725488944E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:18">
+    <row r="184" spans="1:18" ht="17">
       <c r="A184" s="12" t="s">
         <v>343</v>
       </c>
@@ -14018,20 +14063,20 @@
       <c r="O184" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="P184" s="26">
+      <c r="P184" s="20">
         <f t="shared" si="8"/>
         <v>8.990434922769094E-3</v>
       </c>
-      <c r="Q184" s="26">
+      <c r="Q184" s="20">
         <f t="shared" si="9"/>
         <v>1.7319851520788621E-2</v>
       </c>
-      <c r="R184" s="26">
+      <c r="R184" s="20">
         <f t="shared" si="10"/>
         <v>3.9292317421567663E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:18">
+    <row r="185" spans="1:18" ht="17">
       <c r="A185" s="12" t="s">
         <v>348</v>
       </c>
@@ -14077,20 +14122,20 @@
       <c r="O185" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="P185" s="26">
+      <c r="P185" s="20">
         <f t="shared" si="8"/>
         <v>-1.0776716546661567E-2</v>
       </c>
-      <c r="Q185" s="26">
+      <c r="Q185" s="20">
         <f t="shared" si="9"/>
         <v>-1.0476952694079731E-2</v>
       </c>
-      <c r="R185" s="26">
+      <c r="R185" s="20">
         <f t="shared" si="10"/>
         <v>-1.1024978313943098E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:18">
+    <row r="186" spans="1:18" ht="17">
       <c r="A186" s="12" t="s">
         <v>351</v>
       </c>
@@ -14136,20 +14181,20 @@
       <c r="O186" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="P186" s="26">
+      <c r="P186" s="20">
         <f t="shared" si="8"/>
         <v>-4.5229319714723645E-2</v>
       </c>
-      <c r="Q186" s="26">
+      <c r="Q186" s="20">
         <f t="shared" si="9"/>
         <v>-3.8931475621685641E-2</v>
       </c>
-      <c r="R186" s="26">
+      <c r="R186" s="20">
         <f t="shared" si="10"/>
         <v>-3.5315712290992778E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:18">
+    <row r="187" spans="1:18" ht="17">
       <c r="A187" s="12" t="s">
         <v>355</v>
       </c>
@@ -14195,20 +14240,20 @@
       <c r="O187" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="P187" s="26">
+      <c r="P187" s="20">
         <f t="shared" si="8"/>
         <v>-0.115471263776755</v>
       </c>
-      <c r="Q187" s="26">
+      <c r="Q187" s="20">
         <f t="shared" si="9"/>
         <v>-9.3334856239204844E-2</v>
       </c>
-      <c r="R187" s="26">
+      <c r="R187" s="20">
         <f t="shared" si="10"/>
         <v>-8.1654439121027683E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:18">
+    <row r="188" spans="1:18" ht="17">
       <c r="A188" s="12" t="s">
         <v>359</v>
       </c>
@@ -14254,20 +14299,20 @@
       <c r="O188" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="P188" s="26">
+      <c r="P188" s="20">
         <f t="shared" si="8"/>
         <v>-0.12856184485165387</v>
       </c>
-      <c r="Q188" s="26">
+      <c r="Q188" s="20">
         <f t="shared" si="9"/>
         <v>-0.15042389594479841</v>
       </c>
-      <c r="R188" s="26">
+      <c r="R188" s="20">
         <f t="shared" si="10"/>
         <v>-0.12807063681173217</v>
       </c>
     </row>
-    <row r="189" spans="1:18">
+    <row r="189" spans="1:18" ht="17">
       <c r="A189" s="12" t="s">
         <v>361</v>
       </c>
@@ -14313,20 +14358,20 @@
       <c r="O189" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="P189" s="26">
+      <c r="P189" s="20">
         <f t="shared" si="8"/>
         <v>-0.12708959920259383</v>
       </c>
-      <c r="Q189" s="26">
+      <c r="Q189" s="20">
         <f t="shared" si="9"/>
         <v>-0.12713029971498077</v>
       </c>
-      <c r="R189" s="26">
+      <c r="R189" s="20">
         <f t="shared" si="10"/>
         <v>-7.7062196890682236E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:18">
+    <row r="190" spans="1:18" ht="17">
       <c r="A190" s="12" t="s">
         <v>363</v>
       </c>
@@ -14372,20 +14417,20 @@
       <c r="O190" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="P190" s="26">
+      <c r="P190" s="20">
         <f t="shared" si="8"/>
         <v>0.19546049180174055</v>
       </c>
-      <c r="Q190" s="26">
+      <c r="Q190" s="20">
         <f t="shared" si="9"/>
         <v>-6.7745292525820426E-3</v>
       </c>
-      <c r="R190" s="26">
+      <c r="R190" s="20">
         <f t="shared" si="10"/>
         <v>-2.9621787538812429E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:18">
+    <row r="191" spans="1:18" ht="17">
       <c r="A191" s="12" t="s">
         <v>367</v>
       </c>
@@ -14431,20 +14476,20 @@
       <c r="O191" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="P191" s="26">
+      <c r="P191" s="20">
         <f t="shared" si="8"/>
         <v>0.17001559274037545</v>
       </c>
-      <c r="Q191" s="26">
+      <c r="Q191" s="20">
         <f t="shared" si="9"/>
         <v>-7.24829832162633E-2</v>
       </c>
-      <c r="R191" s="26">
+      <c r="R191" s="20">
         <f t="shared" si="10"/>
         <v>-3.8781717687504137E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:18">
+    <row r="192" spans="1:18" ht="17">
       <c r="A192" s="12" t="s">
         <v>369</v>
       </c>
@@ -14490,20 +14535,20 @@
       <c r="O192" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="P192" s="26">
+      <c r="P192" s="20">
         <f t="shared" si="8"/>
         <v>0.3107189584917493</v>
       </c>
-      <c r="Q192" s="26">
+      <c r="Q192" s="20">
         <f t="shared" si="9"/>
         <v>8.0405905220580134E-3</v>
       </c>
-      <c r="R192" s="26">
+      <c r="R192" s="20">
         <f t="shared" si="10"/>
         <v>-8.8599722327506961E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:18">
+    <row r="193" spans="1:18" ht="17">
       <c r="A193" s="12" t="s">
         <v>373</v>
       </c>
@@ -14549,20 +14594,20 @@
       <c r="O193" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="P193" s="26">
+      <c r="P193" s="20">
         <f t="shared" si="8"/>
         <v>0.29709786566238533</v>
       </c>
-      <c r="Q193" s="26">
+      <c r="Q193" s="20">
         <f t="shared" si="9"/>
         <v>-1.591581961804224E-2</v>
       </c>
-      <c r="R193" s="26">
+      <c r="R193" s="20">
         <f t="shared" si="10"/>
         <v>-1.843244366110721E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:18">
+    <row r="194" spans="1:18" ht="17">
       <c r="A194" s="12" t="s">
         <v>379</v>
       </c>
@@ -14608,20 +14653,20 @@
       <c r="O194" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="P194" s="26">
+      <c r="P194" s="20">
         <f t="shared" si="8"/>
         <v>4.8273279501732234E-2</v>
       </c>
-      <c r="Q194" s="26">
+      <c r="Q194" s="20">
         <f t="shared" si="9"/>
         <v>-2.121688302998069E-2</v>
       </c>
-      <c r="R194" s="26">
+      <c r="R194" s="20">
         <f t="shared" si="10"/>
         <v>1.0267007066223494E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:18">
+    <row r="195" spans="1:18" ht="17">
       <c r="A195" s="12" t="s">
         <v>381</v>
       </c>
@@ -14667,20 +14712,20 @@
       <c r="O195" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="P195" s="26">
+      <c r="P195" s="20">
         <f t="shared" si="8"/>
         <v>8.907720497952494E-2</v>
       </c>
-      <c r="Q195" s="26">
+      <c r="Q195" s="20">
         <f t="shared" si="9"/>
         <v>1.5398456723534761E-2</v>
       </c>
-      <c r="R195" s="26">
+      <c r="R195" s="20">
         <f t="shared" si="10"/>
         <v>4.2892609639004028E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:18">
+    <row r="196" spans="1:18" ht="17">
       <c r="A196" s="12" t="s">
         <v>383</v>
       </c>
@@ -14726,20 +14771,20 @@
       <c r="O196" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="P196" s="26">
+      <c r="P196" s="20">
         <f t="shared" si="8"/>
         <v>-0.19757309712841456</v>
       </c>
-      <c r="Q196" s="26">
+      <c r="Q196" s="20">
         <f t="shared" si="9"/>
         <v>9.4377047518890811E-2</v>
       </c>
-      <c r="R196" s="26">
+      <c r="R196" s="20">
         <f t="shared" si="10"/>
         <v>8.9072107134379547E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:18">
+    <row r="197" spans="1:18" ht="17">
       <c r="A197" s="12" t="s">
         <v>386</v>
       </c>
@@ -14785,20 +14830,20 @@
       <c r="O197" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="P197" s="26">
+      <c r="P197" s="20">
         <f t="shared" si="8"/>
         <v>0.10698175120238851</v>
       </c>
-      <c r="Q197" s="26">
+      <c r="Q197" s="20">
         <f t="shared" si="9"/>
         <v>0.17463697718225216</v>
       </c>
-      <c r="R197" s="26">
+      <c r="R197" s="20">
         <f t="shared" si="10"/>
         <v>7.6752775092991249E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:18">
+    <row r="198" spans="1:18" ht="17">
       <c r="A198" s="12" t="s">
         <v>390</v>
       </c>
@@ -14844,20 +14889,20 @@
       <c r="O198" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="P198" s="26">
+      <c r="P198" s="20">
         <f t="shared" si="8"/>
         <v>-7.9926575918619791E-2</v>
       </c>
-      <c r="Q198" s="26">
+      <c r="Q198" s="20">
         <f t="shared" si="9"/>
         <v>-5.5831816249371627E-2</v>
       </c>
-      <c r="R198" s="26">
+      <c r="R198" s="20">
         <f t="shared" si="10"/>
         <v>-4.055181473337819E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:18">
+    <row r="199" spans="1:18" ht="17">
       <c r="A199" s="12" t="s">
         <v>393</v>
       </c>
@@ -14903,20 +14948,20 @@
       <c r="O199" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="P199" s="26">
+      <c r="P199" s="20">
         <f t="shared" si="8"/>
         <v>-2.7370237474267319E-2</v>
       </c>
-      <c r="Q199" s="26">
+      <c r="Q199" s="20">
         <f t="shared" si="9"/>
         <v>-2.7070678682851609E-2</v>
       </c>
-      <c r="R199" s="26">
+      <c r="R199" s="20">
         <f t="shared" si="10"/>
         <v>-1.8743378697742646E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:18">
+    <row r="200" spans="1:18" ht="17">
       <c r="A200" s="12" t="s">
         <v>396</v>
       </c>
@@ -14962,20 +15007,20 @@
       <c r="O200" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="P200" s="26">
+      <c r="P200" s="20">
         <f t="shared" ref="P200:P262" si="11">(B200-B193)/B193</f>
         <v>7.080161447778008E-3</v>
       </c>
-      <c r="Q200" s="26">
+      <c r="Q200" s="20">
         <f t="shared" si="9"/>
         <v>3.6591608658408307E-3</v>
       </c>
-      <c r="R200" s="26">
+      <c r="R200" s="20">
         <f t="shared" si="10"/>
         <v>-2.8442781428962257E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:18">
+    <row r="201" spans="1:18" ht="17">
       <c r="A201" s="12" t="s">
         <v>400</v>
       </c>
@@ -15021,20 +15066,20 @@
       <c r="O201" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="P201" s="26">
+      <c r="P201" s="20">
         <f t="shared" si="11"/>
         <v>-3.1093069707538237E-2</v>
       </c>
-      <c r="Q201" s="26">
+      <c r="Q201" s="20">
         <f t="shared" si="9"/>
         <v>-1.1241609795826663E-2</v>
       </c>
-      <c r="R201" s="26">
+      <c r="R201" s="20">
         <f t="shared" si="10"/>
         <v>1.2338624475800964E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:18">
+    <row r="202" spans="1:18" ht="17">
       <c r="A202" s="12" t="s">
         <v>403</v>
       </c>
@@ -15080,20 +15125,20 @@
       <c r="O202" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="P202" s="26">
+      <c r="P202" s="20">
         <f t="shared" si="11"/>
         <v>-3.1944069214630638E-2</v>
       </c>
-      <c r="Q202" s="26">
+      <c r="Q202" s="20">
         <f t="shared" si="9"/>
         <v>-1.7002416741596246E-2</v>
       </c>
-      <c r="R202" s="26">
+      <c r="R202" s="20">
         <f t="shared" si="10"/>
         <v>2.0374500961494795E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:18">
+    <row r="203" spans="1:18" ht="17">
       <c r="A203" s="12" t="s">
         <v>405</v>
       </c>
@@ -15139,20 +15184,20 @@
       <c r="O203" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="P203" s="26">
+      <c r="P203" s="20">
         <f t="shared" si="11"/>
         <v>-3.6076351526731561E-2</v>
       </c>
-      <c r="Q203" s="26">
+      <c r="Q203" s="20">
         <f t="shared" si="9"/>
         <v>-3.1804963871857848E-2</v>
       </c>
-      <c r="R203" s="26">
+      <c r="R203" s="20">
         <f t="shared" si="10"/>
         <v>-1.7117410081996513E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:18">
+    <row r="204" spans="1:18" ht="17">
       <c r="A204" s="12" t="s">
         <v>177</v>
       </c>
@@ -15198,20 +15243,20 @@
       <c r="O204" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="P204" s="26">
+      <c r="P204" s="20">
         <f t="shared" si="11"/>
         <v>2.0829051544588146E-3</v>
       </c>
-      <c r="Q204" s="26">
+      <c r="Q204" s="20">
         <f t="shared" si="9"/>
         <v>4.2074575371362534E-3</v>
       </c>
-      <c r="R204" s="26">
+      <c r="R204" s="20">
         <f t="shared" si="10"/>
         <v>2.1898308570141582E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:18">
+    <row r="205" spans="1:18" ht="17">
       <c r="A205" s="12" t="s">
         <v>181</v>
       </c>
@@ -15257,20 +15302,20 @@
       <c r="O205" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="P205" s="26">
+      <c r="P205" s="20">
         <f t="shared" si="11"/>
         <v>-3.1578128133084298E-2</v>
       </c>
-      <c r="Q205" s="26">
+      <c r="Q205" s="20">
         <f t="shared" si="9"/>
         <v>4.1910248898518937E-2</v>
       </c>
-      <c r="R205" s="26">
+      <c r="R205" s="20">
         <f t="shared" si="10"/>
         <v>5.5929665962880667E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:18">
+    <row r="206" spans="1:18" ht="17">
       <c r="A206" s="12" t="s">
         <v>183</v>
       </c>
@@ -15316,20 +15361,20 @@
       <c r="O206" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="P206" s="26">
+      <c r="P206" s="20">
         <f t="shared" si="11"/>
         <v>-4.4476900635860378E-2</v>
       </c>
-      <c r="Q206" s="26">
+      <c r="Q206" s="20">
         <f t="shared" ref="Q206:Q263" si="12">(E206-E199)/E199</f>
         <v>-1.0716326707101037E-3</v>
       </c>
-      <c r="R206" s="26">
+      <c r="R206" s="20">
         <f t="shared" ref="R206:R263" si="13">(F206-F199)/F199</f>
         <v>1.4295908731586831E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:18">
+    <row r="207" spans="1:18" ht="17">
       <c r="A207" s="12" t="s">
         <v>188</v>
       </c>
@@ -15375,20 +15420,20 @@
       <c r="O207" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="P207" s="26">
+      <c r="P207" s="20">
         <f t="shared" si="11"/>
         <v>-4.5520711522577965E-2</v>
       </c>
-      <c r="Q207" s="26">
+      <c r="Q207" s="20">
         <f t="shared" si="12"/>
         <v>-1.6167168035386918E-2</v>
       </c>
-      <c r="R207" s="26">
+      <c r="R207" s="20">
         <f t="shared" si="13"/>
         <v>8.7420616224683769E-4</v>
       </c>
     </row>
-    <row r="208" spans="1:18">
+    <row r="208" spans="1:18" ht="17">
       <c r="A208" s="12" t="s">
         <v>194</v>
       </c>
@@ -15434,20 +15479,20 @@
       <c r="O208" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="P208" s="26">
+      <c r="P208" s="20">
         <f t="shared" si="11"/>
         <v>-4.0802958822171907E-2</v>
       </c>
-      <c r="Q208" s="26">
+      <c r="Q208" s="20">
         <f t="shared" si="12"/>
         <v>-5.3099927676144944E-2</v>
       </c>
-      <c r="R208" s="26">
+      <c r="R208" s="20">
         <f t="shared" si="13"/>
         <v>-2.6887062811518321E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:18">
+    <row r="209" spans="1:18" ht="17">
       <c r="A209" s="12" t="s">
         <v>198</v>
       </c>
@@ -15493,20 +15538,20 @@
       <c r="O209" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="P209" s="26">
+      <c r="P209" s="20">
         <f t="shared" si="11"/>
         <v>2.2214301670601049E-2</v>
       </c>
-      <c r="Q209" s="26">
+      <c r="Q209" s="20">
         <f t="shared" si="12"/>
         <v>3.5191174486424149E-3</v>
       </c>
-      <c r="R209" s="26">
+      <c r="R209" s="20">
         <f t="shared" si="13"/>
         <v>1.746969319904812E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:18">
+    <row r="210" spans="1:18" ht="17">
       <c r="A210" s="12" t="s">
         <v>202</v>
       </c>
@@ -15552,20 +15597,20 @@
       <c r="O210" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="P210" s="26">
+      <c r="P210" s="20">
         <f t="shared" si="11"/>
         <v>1.1986786290299438E-2</v>
       </c>
-      <c r="Q210" s="26">
+      <c r="Q210" s="20">
         <f t="shared" si="12"/>
         <v>1.1456499232849856E-2</v>
       </c>
-      <c r="R210" s="26">
+      <c r="R210" s="20">
         <f t="shared" si="13"/>
         <v>2.2032714662974223E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:18">
+    <row r="211" spans="1:18" ht="17">
       <c r="A211" s="12" t="s">
         <v>207</v>
       </c>
@@ -15611,20 +15656,20 @@
       <c r="O211" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="P211" s="26">
+      <c r="P211" s="20">
         <f t="shared" si="11"/>
         <v>-2.1762498103559492E-2</v>
       </c>
-      <c r="Q211" s="26">
+      <c r="Q211" s="20">
         <f t="shared" si="12"/>
         <v>-1.1095603641015717E-2</v>
       </c>
-      <c r="R211" s="26">
+      <c r="R211" s="20">
         <f t="shared" si="13"/>
         <v>-1.5205505231359249E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:18">
+    <row r="212" spans="1:18" ht="17">
       <c r="A212" s="12" t="s">
         <v>212</v>
       </c>
@@ -15670,20 +15715,20 @@
       <c r="O212" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="P212" s="26">
+      <c r="P212" s="20">
         <f t="shared" si="11"/>
         <v>1.2776200412475024E-2</v>
       </c>
-      <c r="Q212" s="26">
+      <c r="Q212" s="20">
         <f t="shared" si="12"/>
         <v>-3.4222882460408326E-2</v>
       </c>
-      <c r="R212" s="26">
+      <c r="R212" s="20">
         <f t="shared" si="13"/>
         <v>-4.231255133197085E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:18">
+    <row r="213" spans="1:18" ht="17">
       <c r="A213" s="12" t="s">
         <v>215</v>
       </c>
@@ -15729,20 +15774,20 @@
       <c r="O213" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="P213" s="26">
+      <c r="P213" s="20">
         <f t="shared" si="11"/>
         <v>3.1222064363423896E-2</v>
       </c>
-      <c r="Q213" s="26">
+      <c r="Q213" s="20">
         <f t="shared" si="12"/>
         <v>5.1162433698573161E-3</v>
       </c>
-      <c r="R213" s="26">
+      <c r="R213" s="20">
         <f t="shared" si="13"/>
         <v>-7.6475028255852005E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:18">
+    <row r="214" spans="1:18" ht="17">
       <c r="A214" s="12" t="s">
         <v>221</v>
       </c>
@@ -15788,20 +15833,20 @@
       <c r="O214" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="P214" s="26">
+      <c r="P214" s="20">
         <f t="shared" si="11"/>
         <v>2.3194728273895206E-2</v>
       </c>
-      <c r="Q214" s="26">
+      <c r="Q214" s="20">
         <f t="shared" si="12"/>
         <v>1.8985504261124945E-2</v>
       </c>
-      <c r="R214" s="26">
+      <c r="R214" s="20">
         <f t="shared" si="13"/>
         <v>1.2331251247350865E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:18">
+    <row r="215" spans="1:18" ht="17">
       <c r="A215" s="12" t="s">
         <v>226</v>
       </c>
@@ -15847,20 +15892,20 @@
       <c r="O215" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="P215" s="26">
+      <c r="P215" s="20">
         <f t="shared" si="11"/>
         <v>5.3650986781403828E-2</v>
       </c>
-      <c r="Q215" s="26">
+      <c r="Q215" s="20">
         <f t="shared" si="12"/>
         <v>6.0429707278928518E-2</v>
       </c>
-      <c r="R215" s="26">
+      <c r="R215" s="20">
         <f t="shared" si="13"/>
         <v>2.5099738635953914E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:18">
+    <row r="216" spans="1:18" ht="17">
       <c r="A216" s="12" t="s">
         <v>230</v>
       </c>
@@ -15906,20 +15951,20 @@
       <c r="O216" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="P216" s="26">
+      <c r="P216" s="20">
         <f t="shared" si="11"/>
         <v>-1.6954762628783966E-3</v>
       </c>
-      <c r="Q216" s="26">
+      <c r="Q216" s="20">
         <f t="shared" si="12"/>
         <v>1.1479372743829954E-2</v>
       </c>
-      <c r="R216" s="26">
+      <c r="R216" s="20">
         <f t="shared" si="13"/>
         <v>-6.3470952277877067E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:18">
+    <row r="217" spans="1:18" ht="17">
       <c r="A217" s="12" t="s">
         <v>233</v>
       </c>
@@ -15965,20 +16010,20 @@
       <c r="O217" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="P217" s="26">
+      <c r="P217" s="20">
         <f t="shared" si="11"/>
         <v>-2.284550571669213E-3</v>
       </c>
-      <c r="Q217" s="26">
+      <c r="Q217" s="20">
         <f t="shared" si="12"/>
         <v>-1.2348542493720284E-2</v>
       </c>
-      <c r="R217" s="26">
+      <c r="R217" s="20">
         <f t="shared" si="13"/>
         <v>-3.0551322497656359E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:18">
+    <row r="218" spans="1:18" ht="17">
       <c r="A218" s="12" t="s">
         <v>237</v>
       </c>
@@ -16024,20 +16069,20 @@
       <c r="O218" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="P218" s="26">
+      <c r="P218" s="20">
         <f t="shared" si="11"/>
         <v>9.3781721196039662E-3</v>
       </c>
-      <c r="Q218" s="26">
+      <c r="Q218" s="20">
         <f t="shared" si="12"/>
         <v>-1.2213237123662603E-2</v>
       </c>
-      <c r="R218" s="26">
+      <c r="R218" s="20">
         <f t="shared" si="13"/>
         <v>-2.3942235909677929E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:18">
+    <row r="219" spans="1:18" ht="17">
       <c r="A219" s="12" t="s">
         <v>239</v>
       </c>
@@ -16083,20 +16128,20 @@
       <c r="O219" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="P219" s="26">
+      <c r="P219" s="20">
         <f t="shared" si="11"/>
         <v>-1.149664298701077E-2</v>
       </c>
-      <c r="Q219" s="26">
+      <c r="Q219" s="20">
         <f t="shared" si="12"/>
         <v>-7.1746396381430627E-2</v>
       </c>
-      <c r="R219" s="26">
+      <c r="R219" s="20">
         <f t="shared" si="13"/>
         <v>-7.899054077155393E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:18">
+    <row r="220" spans="1:18" ht="17">
       <c r="A220" s="12" t="s">
         <v>244</v>
       </c>
@@ -16142,20 +16187,20 @@
       <c r="O220" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="P220" s="26">
+      <c r="P220" s="20">
         <f t="shared" si="11"/>
         <v>8.1305617884821254E-4</v>
       </c>
-      <c r="Q220" s="26">
+      <c r="Q220" s="20">
         <f t="shared" si="12"/>
         <v>-3.3581117109245516E-2</v>
       </c>
-      <c r="R220" s="26">
+      <c r="R220" s="20">
         <f t="shared" si="13"/>
         <v>-2.556252748424746E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:18">
+    <row r="221" spans="1:18" ht="17">
       <c r="A221" s="12" t="s">
         <v>249</v>
       </c>
@@ -16201,20 +16246,20 @@
       <c r="O221" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="P221" s="26">
+      <c r="P221" s="20">
         <f t="shared" si="11"/>
         <v>0.12527212734693449</v>
       </c>
-      <c r="Q221" s="26">
+      <c r="Q221" s="20">
         <f t="shared" si="12"/>
         <v>8.4524514496637698E-2</v>
       </c>
-      <c r="R221" s="26">
+      <c r="R221" s="20">
         <f t="shared" si="13"/>
         <v>-1.4126678043581387E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:18">
+    <row r="222" spans="1:18" ht="17">
       <c r="A222" s="12" t="s">
         <v>254</v>
       </c>
@@ -16260,20 +16305,20 @@
       <c r="O222" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="P222" s="26">
+      <c r="P222" s="20">
         <f t="shared" si="11"/>
         <v>0.19144529000343666</v>
       </c>
-      <c r="Q222" s="26">
+      <c r="Q222" s="20">
         <f t="shared" si="12"/>
         <v>0.15220382357514653</v>
       </c>
-      <c r="R222" s="26">
+      <c r="R222" s="20">
         <f t="shared" si="13"/>
         <v>1.4756414035037272E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:18">
+    <row r="223" spans="1:18" ht="17">
       <c r="A223" s="12" t="s">
         <v>260</v>
       </c>
@@ -16319,20 +16364,20 @@
       <c r="O223" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="P223" s="26">
+      <c r="P223" s="20">
         <f t="shared" si="11"/>
         <v>0.12902351815423138</v>
       </c>
-      <c r="Q223" s="26">
+      <c r="Q223" s="20">
         <f t="shared" si="12"/>
         <v>0.12975399602103671</v>
       </c>
-      <c r="R223" s="26">
+      <c r="R223" s="20">
         <f t="shared" si="13"/>
         <v>-1.7681544504539268E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:18">
+    <row r="224" spans="1:18" ht="17">
       <c r="A224" s="12" t="s">
         <v>263</v>
       </c>
@@ -16378,20 +16423,20 @@
       <c r="O224" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="P224" s="26">
+      <c r="P224" s="20">
         <f t="shared" si="11"/>
         <v>0.43750455446532444</v>
       </c>
-      <c r="Q224" s="26">
+      <c r="Q224" s="20">
         <f t="shared" si="12"/>
         <v>0.16511396229525496</v>
       </c>
-      <c r="R224" s="26">
+      <c r="R224" s="20">
         <f t="shared" si="13"/>
         <v>2.029345548134415E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:18">
+    <row r="225" spans="1:18" ht="17">
       <c r="A225" s="12" t="s">
         <v>264</v>
       </c>
@@ -16437,20 +16482,20 @@
       <c r="O225" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="P225" s="26">
+      <c r="P225" s="20">
         <f t="shared" si="11"/>
         <v>9.1243009305174413E-2</v>
       </c>
-      <c r="Q225" s="26">
+      <c r="Q225" s="20">
         <f t="shared" si="12"/>
         <v>0.16012739387547162</v>
       </c>
-      <c r="R225" s="26">
+      <c r="R225" s="20">
         <f t="shared" si="13"/>
         <v>2.0212906773948967E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:18">
+    <row r="226" spans="1:18" ht="17">
       <c r="A226" s="12" t="s">
         <v>268</v>
       </c>
@@ -16496,20 +16541,20 @@
       <c r="O226" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="P226" s="26">
+      <c r="P226" s="20">
         <f t="shared" si="11"/>
         <v>8.1828021246827365E-2</v>
       </c>
-      <c r="Q226" s="26">
+      <c r="Q226" s="20">
         <f t="shared" si="12"/>
         <v>0.21101238667500313</v>
       </c>
-      <c r="R226" s="26">
+      <c r="R226" s="20">
         <f t="shared" si="13"/>
         <v>7.4876282227176669E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:18">
+    <row r="227" spans="1:18" ht="17">
       <c r="A227" s="12" t="s">
         <v>271</v>
       </c>
@@ -16555,20 +16600,20 @@
       <c r="O227" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="P227" s="26">
+      <c r="P227" s="20">
         <f t="shared" si="11"/>
         <v>-0.10356601937732228</v>
       </c>
-      <c r="Q227" s="26">
+      <c r="Q227" s="20">
         <f t="shared" si="12"/>
         <v>0.12921285598121954</v>
       </c>
-      <c r="R227" s="26">
+      <c r="R227" s="20">
         <f t="shared" si="13"/>
         <v>1.4788564547085315E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:18">
+    <row r="228" spans="1:18" ht="17">
       <c r="A228" s="12" t="s">
         <v>273</v>
       </c>
@@ -16614,20 +16659,20 @@
       <c r="O228" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="P228" s="26">
+      <c r="P228" s="20">
         <f t="shared" si="11"/>
         <v>-2.7700226059886156E-2</v>
       </c>
-      <c r="Q228" s="26">
+      <c r="Q228" s="20">
         <f t="shared" si="12"/>
         <v>1.6385253683704745E-2</v>
       </c>
-      <c r="R228" s="26">
+      <c r="R228" s="20">
         <f t="shared" si="13"/>
         <v>1.1203676591368438E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:18">
+    <row r="229" spans="1:18" ht="17">
       <c r="A229" s="12" t="s">
         <v>276</v>
       </c>
@@ -16673,20 +16718,20 @@
       <c r="O229" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="P229" s="26">
+      <c r="P229" s="20">
         <f t="shared" si="11"/>
         <v>3.9456816509053638E-3</v>
       </c>
-      <c r="Q229" s="26">
+      <c r="Q229" s="20">
         <f t="shared" si="12"/>
         <v>-5.215493144468052E-3</v>
       </c>
-      <c r="R229" s="26">
+      <c r="R229" s="20">
         <f t="shared" si="13"/>
         <v>-3.0402559981217089E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:18">
+    <row r="230" spans="1:18" ht="17">
       <c r="A230" s="12" t="s">
         <v>282</v>
       </c>
@@ -16732,20 +16777,20 @@
       <c r="O230" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="P230" s="26">
+      <c r="P230" s="20">
         <f t="shared" si="11"/>
         <v>8.0226185393482904E-2</v>
       </c>
-      <c r="Q230" s="26">
+      <c r="Q230" s="20">
         <f t="shared" si="12"/>
         <v>6.1668828941678223E-2</v>
       </c>
-      <c r="R230" s="26">
+      <c r="R230" s="20">
         <f t="shared" si="13"/>
         <v>3.6652103340181257E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:18">
+    <row r="231" spans="1:18" ht="17">
       <c r="A231" s="12" t="s">
         <v>287</v>
       </c>
@@ -16791,20 +16836,20 @@
       <c r="O231" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="P231" s="26">
+      <c r="P231" s="20">
         <f t="shared" si="11"/>
         <v>7.1325041556856289E-2</v>
       </c>
-      <c r="Q231" s="26">
+      <c r="Q231" s="20">
         <f t="shared" si="12"/>
         <v>3.8868255870703118E-2</v>
       </c>
-      <c r="R231" s="26">
+      <c r="R231" s="20">
         <f t="shared" si="13"/>
         <v>4.3639949722986855E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:18">
+    <row r="232" spans="1:18" ht="17">
       <c r="A232" s="12" t="s">
         <v>290</v>
       </c>
@@ -16850,20 +16895,20 @@
       <c r="O232" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="P232" s="26">
+      <c r="P232" s="20">
         <f t="shared" si="11"/>
         <v>1.0324513883246135E-2</v>
       </c>
-      <c r="Q232" s="26">
+      <c r="Q232" s="20">
         <f t="shared" si="12"/>
         <v>3.8570996533728299E-3</v>
       </c>
-      <c r="R232" s="26">
+      <c r="R232" s="20">
         <f t="shared" si="13"/>
         <v>2.2299037769906219E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:18">
+    <row r="233" spans="1:18" ht="17">
       <c r="A233" s="12" t="s">
         <v>292</v>
       </c>
@@ -16909,20 +16954,20 @@
       <c r="O233" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P233" s="26">
+      <c r="P233" s="20">
         <f t="shared" si="11"/>
         <v>-4.5085212875150896E-2</v>
       </c>
-      <c r="Q233" s="26">
+      <c r="Q233" s="20">
         <f t="shared" si="12"/>
         <v>-4.6803760932964303E-2</v>
       </c>
-      <c r="R233" s="26">
+      <c r="R233" s="20">
         <f t="shared" si="13"/>
         <v>-8.9244779472520738E-3</v>
       </c>
     </row>
-    <row r="234" spans="1:18">
+    <row r="234" spans="1:18" ht="17">
       <c r="A234" s="12" t="s">
         <v>295</v>
       </c>
@@ -16968,20 +17013,20 @@
       <c r="O234" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="P234" s="26">
+      <c r="P234" s="20">
         <f t="shared" si="11"/>
         <v>-9.1397238636111267E-2</v>
       </c>
-      <c r="Q234" s="26">
+      <c r="Q234" s="20">
         <f t="shared" si="12"/>
         <v>-7.7300307995369397E-2</v>
       </c>
-      <c r="R234" s="26">
+      <c r="R234" s="20">
         <f t="shared" si="13"/>
         <v>-4.9064909346456374E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:18">
+    <row r="235" spans="1:18" ht="17">
       <c r="A235" s="6" t="s">
         <v>22</v>
       </c>
@@ -17027,20 +17072,20 @@
       <c r="O235" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="P235" s="26">
+      <c r="P235" s="20">
         <f t="shared" si="11"/>
         <v>-0.26256659975841906</v>
       </c>
-      <c r="Q235" s="26">
+      <c r="Q235" s="20">
         <f t="shared" si="12"/>
         <v>-0.21017085325475951</v>
       </c>
-      <c r="R235" s="26">
+      <c r="R235" s="20">
         <f t="shared" si="13"/>
         <v>-0.16819661498566574</v>
       </c>
     </row>
-    <row r="236" spans="1:18">
+    <row r="236" spans="1:18" ht="17">
       <c r="A236" s="6" t="s">
         <v>29</v>
       </c>
@@ -17086,20 +17131,20 @@
       <c r="O236" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="P236" s="26">
+      <c r="P236" s="20">
         <f t="shared" si="11"/>
         <v>-0.53685111013165121</v>
       </c>
-      <c r="Q236" s="26">
+      <c r="Q236" s="20">
         <f t="shared" si="12"/>
         <v>-0.48280780391165828</v>
       </c>
-      <c r="R236" s="26">
+      <c r="R236" s="20">
         <f t="shared" si="13"/>
         <v>-0.3261578629576225</v>
       </c>
     </row>
-    <row r="237" spans="1:18">
+    <row r="237" spans="1:18" ht="17">
       <c r="A237" s="6" t="s">
         <v>34</v>
       </c>
@@ -17145,20 +17190,20 @@
       <c r="O237" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="P237" s="26">
+      <c r="P237" s="20">
         <f t="shared" si="11"/>
         <v>-0.49755024400597087</v>
       </c>
-      <c r="Q237" s="26">
+      <c r="Q237" s="20">
         <f t="shared" si="12"/>
         <v>-0.46162390467234454</v>
       </c>
-      <c r="R237" s="26">
+      <c r="R237" s="20">
         <f t="shared" si="13"/>
         <v>-0.31697739628532928</v>
       </c>
     </row>
-    <row r="238" spans="1:18">
+    <row r="238" spans="1:18" ht="17">
       <c r="A238" s="6" t="s">
         <v>40</v>
       </c>
@@ -17204,20 +17249,20 @@
       <c r="O238" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="P238" s="26">
+      <c r="P238" s="20">
         <f t="shared" si="11"/>
         <v>-0.32001581662232303</v>
       </c>
-      <c r="Q238" s="26">
+      <c r="Q238" s="20">
         <f t="shared" si="12"/>
         <v>-0.29399244994588863</v>
       </c>
-      <c r="R238" s="26">
+      <c r="R238" s="20">
         <f t="shared" si="13"/>
         <v>-0.15826603314950347</v>
       </c>
     </row>
-    <row r="239" spans="1:18">
+    <row r="239" spans="1:18" ht="17">
       <c r="A239" s="6" t="s">
         <v>47</v>
       </c>
@@ -17263,20 +17308,20 @@
       <c r="O239" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="P239" s="26">
+      <c r="P239" s="20">
         <f t="shared" si="11"/>
         <v>-2.2772052952313108E-2</v>
       </c>
-      <c r="Q239" s="26">
+      <c r="Q239" s="20">
         <f t="shared" si="12"/>
         <v>-3.1793589093920327E-2</v>
       </c>
-      <c r="R239" s="26">
+      <c r="R239" s="20">
         <f t="shared" si="13"/>
         <v>-2.9594273216998208E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:18">
+    <row r="240" spans="1:18" ht="17">
       <c r="A240" s="6" t="s">
         <v>54</v>
       </c>
@@ -17322,20 +17367,20 @@
       <c r="O240" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P240" s="26">
+      <c r="P240" s="20">
         <f t="shared" si="11"/>
         <v>1.6882149058082655E-4</v>
       </c>
-      <c r="Q240" s="26">
+      <c r="Q240" s="20">
         <f t="shared" si="12"/>
         <v>3.9401093736573023E-2</v>
       </c>
-      <c r="R240" s="26">
+      <c r="R240" s="20">
         <f t="shared" si="13"/>
         <v>2.0432153402609832E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:18">
+    <row r="241" spans="1:18" ht="17">
       <c r="A241" s="6" t="s">
         <v>60</v>
       </c>
@@ -17381,20 +17426,20 @@
       <c r="O241" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="P241" s="26">
+      <c r="P241" s="20">
         <f t="shared" si="11"/>
         <v>5.7066741411540653E-2</v>
       </c>
-      <c r="Q241" s="26">
+      <c r="Q241" s="20">
         <f t="shared" si="12"/>
         <v>7.076823157794486E-2</v>
       </c>
-      <c r="R241" s="26">
+      <c r="R241" s="20">
         <f t="shared" si="13"/>
         <v>6.6021897454396558E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:18">
+    <row r="242" spans="1:18" ht="17">
       <c r="A242" s="6" t="s">
         <v>66</v>
       </c>
@@ -17440,20 +17485,20 @@
       <c r="O242" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="P242" s="26">
+      <c r="P242" s="20">
         <f t="shared" si="11"/>
         <v>0.27196033457927776</v>
       </c>
-      <c r="Q242" s="26">
+      <c r="Q242" s="20">
         <f t="shared" si="12"/>
         <v>0.24152524456855801</v>
       </c>
-      <c r="R242" s="26">
+      <c r="R242" s="20">
         <f t="shared" si="13"/>
         <v>0.20775660900956486</v>
       </c>
     </row>
-    <row r="243" spans="1:18">
+    <row r="243" spans="1:18" ht="17">
       <c r="A243" s="6" t="s">
         <v>72</v>
       </c>
@@ -17499,20 +17544,20 @@
       <c r="O243" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="P243" s="26">
+      <c r="P243" s="20">
         <f t="shared" si="11"/>
         <v>0.89967184695961322</v>
       </c>
-      <c r="Q243" s="26">
+      <c r="Q243" s="20">
         <f t="shared" si="12"/>
         <v>0.7956737363166525</v>
       </c>
-      <c r="R243" s="26">
+      <c r="R243" s="20">
         <f t="shared" si="13"/>
         <v>0.42818386102577943</v>
       </c>
     </row>
-    <row r="244" spans="1:18">
+    <row r="244" spans="1:18" ht="17">
       <c r="A244" s="6" t="s">
         <v>77</v>
       </c>
@@ -17558,20 +17603,20 @@
       <c r="O244" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="P244" s="26">
+      <c r="P244" s="20">
         <f t="shared" si="11"/>
         <v>0.74112355168152244</v>
       </c>
-      <c r="Q244" s="26">
+      <c r="Q244" s="20">
         <f t="shared" si="12"/>
         <v>0.71675103621529068</v>
       </c>
-      <c r="R244" s="26">
+      <c r="R244" s="20">
         <f t="shared" si="13"/>
         <v>0.38479343771754698</v>
       </c>
     </row>
-    <row r="245" spans="1:18">
+    <row r="245" spans="1:18" ht="17">
       <c r="A245" s="6" t="s">
         <v>83</v>
       </c>
@@ -17617,20 +17662,20 @@
       <c r="O245" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="P245" s="26">
+      <c r="P245" s="20">
         <f t="shared" si="11"/>
         <v>0.34278951287635939</v>
       </c>
-      <c r="Q245" s="26">
+      <c r="Q245" s="20">
         <f t="shared" si="12"/>
         <v>0.34125801209094525</v>
       </c>
-      <c r="R245" s="26">
+      <c r="R245" s="20">
         <f t="shared" si="13"/>
         <v>0.14750125931554814</v>
       </c>
     </row>
-    <row r="246" spans="1:18">
+    <row r="246" spans="1:18" ht="17">
       <c r="A246" s="6" t="s">
         <v>88</v>
       </c>
@@ -17676,20 +17721,20 @@
       <c r="O246" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="P246" s="26">
+      <c r="P246" s="20">
         <f t="shared" si="11"/>
         <v>-2.0475259518700602E-2</v>
       </c>
-      <c r="Q246" s="26">
+      <c r="Q246" s="20">
         <f t="shared" si="12"/>
         <v>5.7833749193584288E-3</v>
       </c>
-      <c r="R246" s="26">
+      <c r="R246" s="20">
         <f t="shared" si="13"/>
         <v>1.6397425661629147E-3</v>
       </c>
     </row>
-    <row r="247" spans="1:18">
+    <row r="247" spans="1:18" ht="17">
       <c r="A247" s="6" t="s">
         <v>94</v>
       </c>
@@ -17735,20 +17780,20 @@
       <c r="O247" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="P247" s="26">
+      <c r="P247" s="20">
         <f t="shared" si="11"/>
         <v>4.8055818145615013E-2</v>
       </c>
-      <c r="Q247" s="26">
+      <c r="Q247" s="20">
         <f t="shared" si="12"/>
         <v>-2.4817888790152214E-2</v>
       </c>
-      <c r="R247" s="26">
+      <c r="R247" s="20">
         <f t="shared" si="13"/>
         <v>-1.2213029660052272E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:18">
+    <row r="248" spans="1:18" ht="17">
       <c r="A248" s="6" t="s">
         <v>101</v>
       </c>
@@ -17794,20 +17839,20 @@
       <c r="O248" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="P248" s="26">
+      <c r="P248" s="20">
         <f t="shared" si="11"/>
         <v>9.4062502035548973E-2</v>
       </c>
-      <c r="Q248" s="26">
+      <c r="Q248" s="20">
         <f t="shared" si="12"/>
         <v>0.18102837175124703</v>
       </c>
-      <c r="R248" s="26">
+      <c r="R248" s="20">
         <f t="shared" si="13"/>
         <v>0.20224472475050484</v>
       </c>
     </row>
-    <row r="249" spans="1:18">
+    <row r="249" spans="1:18" ht="17">
       <c r="A249" s="6" t="s">
         <v>104</v>
       </c>
@@ -17853,20 +17898,20 @@
       <c r="O249" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="P249" s="26">
+      <c r="P249" s="20">
         <f t="shared" si="11"/>
         <v>-0.22241928726251145</v>
       </c>
-      <c r="Q249" s="26">
+      <c r="Q249" s="20">
         <f t="shared" si="12"/>
         <v>-0.16197732358809847</v>
       </c>
-      <c r="R249" s="26">
+      <c r="R249" s="20">
         <f t="shared" si="13"/>
         <v>6.5632249900405407E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:18">
+    <row r="250" spans="1:18" ht="17">
       <c r="A250" s="6" t="s">
         <v>110</v>
       </c>
@@ -17912,20 +17957,20 @@
       <c r="O250" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="P250" s="26">
+      <c r="P250" s="20">
         <f t="shared" si="11"/>
         <v>-0.24914802238087858</v>
       </c>
-      <c r="Q250" s="26">
+      <c r="Q250" s="20">
         <f t="shared" si="12"/>
         <v>-0.29469230711995287</v>
       </c>
-      <c r="R250" s="26">
+      <c r="R250" s="20">
         <f t="shared" si="13"/>
         <v>5.0103141085291493E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:18">
+    <row r="251" spans="1:18" ht="17">
       <c r="A251" s="6" t="s">
         <v>113</v>
       </c>
@@ -17971,20 +18016,20 @@
       <c r="O251" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="P251" s="26">
+      <c r="P251" s="20">
         <f t="shared" si="11"/>
         <v>0.17482662741459079</v>
       </c>
-      <c r="Q251" s="26">
+      <c r="Q251" s="20">
         <f t="shared" si="12"/>
         <v>8.3347593280571022E-2</v>
       </c>
-      <c r="R251" s="26">
+      <c r="R251" s="20">
         <f t="shared" si="13"/>
         <v>8.5699692990361717E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:18">
+    <row r="252" spans="1:18" ht="17">
       <c r="A252" s="6" t="s">
         <v>118</v>
       </c>
@@ -18030,20 +18075,20 @@
       <c r="O252" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="P252" s="26">
+      <c r="P252" s="20">
         <f t="shared" si="11"/>
         <v>8.3325557426151595E-2</v>
       </c>
-      <c r="Q252" s="26">
+      <c r="Q252" s="20">
         <f t="shared" si="12"/>
         <v>4.8001930510906551E-2</v>
       </c>
-      <c r="R252" s="26">
+      <c r="R252" s="20">
         <f t="shared" si="13"/>
         <v>5.3801736050552072E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:18">
+    <row r="253" spans="1:18" ht="17">
       <c r="A253" s="6" t="s">
         <v>124</v>
       </c>
@@ -18089,20 +18134,20 @@
       <c r="O253" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="P253" s="26">
+      <c r="P253" s="20">
         <f t="shared" si="11"/>
         <v>0.18894233965570945</v>
       </c>
-      <c r="Q253" s="26">
+      <c r="Q253" s="20">
         <f t="shared" si="12"/>
         <v>8.2074536110622376E-2</v>
       </c>
-      <c r="R253" s="26">
+      <c r="R253" s="20">
         <f t="shared" si="13"/>
         <v>9.735729690084366E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:18">
+    <row r="254" spans="1:18" ht="17">
       <c r="A254" s="6" t="s">
         <v>129</v>
       </c>
@@ -18148,20 +18193,20 @@
       <c r="O254" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="P254" s="26">
+      <c r="P254" s="20">
         <f t="shared" si="11"/>
         <v>4.0440544133266802E-2</v>
       </c>
-      <c r="Q254" s="26">
+      <c r="Q254" s="20">
         <f t="shared" si="12"/>
         <v>8.9922060823218242E-2</v>
       </c>
-      <c r="R254" s="26">
+      <c r="R254" s="20">
         <f t="shared" si="13"/>
         <v>6.5572641712733609E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:18">
+    <row r="255" spans="1:18" ht="17">
       <c r="A255" s="6" t="s">
         <v>133</v>
       </c>
@@ -18207,20 +18252,20 @@
       <c r="O255" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="P255" s="26">
+      <c r="P255" s="20">
         <f t="shared" si="11"/>
         <v>-0.19491182677190591</v>
       </c>
-      <c r="Q255" s="26">
+      <c r="Q255" s="20">
         <f t="shared" si="12"/>
         <v>-0.12344240032216282</v>
       </c>
-      <c r="R255" s="26">
+      <c r="R255" s="20">
         <f t="shared" si="13"/>
         <v>-0.13655736640741326</v>
       </c>
     </row>
-    <row r="256" spans="1:18">
+    <row r="256" spans="1:18" ht="17">
       <c r="A256" s="6" t="s">
         <v>137</v>
       </c>
@@ -18266,20 +18311,20 @@
       <c r="O256" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="P256" s="26">
+      <c r="P256" s="20">
         <f t="shared" si="11"/>
         <v>0.11713866002999185</v>
       </c>
-      <c r="Q256" s="26">
+      <c r="Q256" s="20">
         <f t="shared" si="12"/>
         <v>0.21386158941470768</v>
       </c>
-      <c r="R256" s="26">
+      <c r="R256" s="20">
         <f t="shared" si="13"/>
         <v>-3.9980780109832657E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:18">
+    <row r="257" spans="1:18" ht="17">
       <c r="A257" s="6" t="s">
         <v>143</v>
       </c>
@@ -18325,20 +18370,20 @@
       <c r="O257" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="P257" s="26">
+      <c r="P257" s="20">
         <f t="shared" si="11"/>
         <v>0.52541420995094124</v>
       </c>
-      <c r="Q257" s="26">
+      <c r="Q257" s="20">
         <f t="shared" si="12"/>
         <v>0.50315719400816705</v>
       </c>
-      <c r="R257" s="26">
+      <c r="R257" s="20">
         <f t="shared" si="13"/>
         <v>2.6075281310838794E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:18">
+    <row r="258" spans="1:18" ht="17">
       <c r="A258" s="6" t="s">
         <v>149</v>
       </c>
@@ -18384,20 +18429,20 @@
       <c r="O258" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P258" s="26">
+      <c r="P258" s="20">
         <f t="shared" si="11"/>
         <v>-2.3237183292441597E-2</v>
       </c>
-      <c r="Q258" s="26">
+      <c r="Q258" s="20">
         <f t="shared" si="12"/>
         <v>-2.7802334412453642E-2</v>
       </c>
-      <c r="R258" s="26">
+      <c r="R258" s="20">
         <f t="shared" si="13"/>
         <v>-4.7563472851373583E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:18">
+    <row r="259" spans="1:18" ht="17">
       <c r="A259" s="6" t="s">
         <v>154</v>
       </c>
@@ -18443,20 +18488,20 @@
       <c r="O259" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="P259" s="26">
+      <c r="P259" s="20">
         <f t="shared" si="11"/>
         <v>-3.7486537597605375E-2</v>
       </c>
-      <c r="Q259" s="26">
+      <c r="Q259" s="20">
         <f t="shared" si="12"/>
         <v>-1.1673946430697312E-2</v>
       </c>
-      <c r="R259" s="26">
+      <c r="R259" s="20">
         <f t="shared" si="13"/>
         <v>-8.787834884544609E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:18">
+    <row r="260" spans="1:18" ht="17">
       <c r="A260" s="6" t="s">
         <v>159</v>
       </c>
@@ -18502,20 +18547,20 @@
       <c r="O260" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="P260" s="26">
+      <c r="P260" s="20">
         <f t="shared" si="11"/>
         <v>-8.952351282413662E-2</v>
       </c>
-      <c r="Q260" s="26">
+      <c r="Q260" s="20">
         <f t="shared" si="12"/>
         <v>-3.9120135274480487E-2</v>
       </c>
-      <c r="R260" s="26">
+      <c r="R260" s="20">
         <f t="shared" si="13"/>
         <v>-4.2647148144349709E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:18">
+    <row r="261" spans="1:18" ht="17">
       <c r="A261" s="6" t="s">
         <v>163</v>
       </c>
@@ -18561,20 +18606,20 @@
       <c r="O261" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="P261" s="26">
+      <c r="P261" s="20">
         <f t="shared" si="11"/>
         <v>-2.1867452338117536E-2</v>
       </c>
-      <c r="Q261" s="26">
+      <c r="Q261" s="20">
         <f t="shared" si="12"/>
         <v>-4.1684869876718558E-2</v>
       </c>
-      <c r="R261" s="26">
+      <c r="R261" s="20">
         <f t="shared" si="13"/>
         <v>-2.8484786709496814E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:18">
+    <row r="262" spans="1:18" ht="17">
       <c r="A262" s="6" t="s">
         <v>167</v>
       </c>
@@ -18620,20 +18665,20 @@
       <c r="O262" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="P262" s="26">
+      <c r="P262" s="20">
         <f t="shared" si="11"/>
         <v>-3.4338049089768646E-2</v>
       </c>
-      <c r="Q262" s="26">
+      <c r="Q262" s="20">
         <f t="shared" si="12"/>
         <v>-4.0910786820404221E-2</v>
       </c>
-      <c r="R262" s="26">
+      <c r="R262" s="20">
         <f t="shared" si="13"/>
         <v>-3.1042847493465683E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:18">
+    <row r="263" spans="1:18" ht="17">
       <c r="A263" s="6" t="s">
         <v>172</v>
       </c>
@@ -18679,17 +18724,489 @@
       <c r="O263" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="P263" s="26">
+      <c r="P263" s="20">
         <f>(B263-B256)/B256</f>
         <v>3.586307770482332E-3</v>
       </c>
-      <c r="Q263" s="26">
+      <c r="Q263" s="20">
         <f t="shared" si="12"/>
         <v>-4.805889217228747E-3</v>
       </c>
-      <c r="R263" s="26">
+      <c r="R263" s="20">
         <f t="shared" si="13"/>
         <v>1.9527827440434398E-4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" ht="22" customHeight="1">
+      <c r="A264" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="B264" s="13">
+        <v>217018238169</v>
+      </c>
+      <c r="C264" s="13">
+        <v>220013927248</v>
+      </c>
+      <c r="D264" s="13">
+        <v>2995689079</v>
+      </c>
+      <c r="E264" s="13">
+        <v>6965125</v>
+      </c>
+      <c r="F264" s="13">
+        <v>3981121</v>
+      </c>
+      <c r="G264" s="13">
+        <v>55264</v>
+      </c>
+      <c r="H264" s="13">
+        <v>31588</v>
+      </c>
+      <c r="I264" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J264" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K264" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="L264" s="15" t="s">
+        <v>818</v>
+      </c>
+      <c r="M264" s="15" t="s">
+        <v>819</v>
+      </c>
+      <c r="N264" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="O264" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="P264" s="20">
+        <f t="shared" ref="P264:P271" si="14">(B264-B257)/B257</f>
+        <v>5.0403437323324855E-3</v>
+      </c>
+      <c r="Q264" s="20">
+        <f t="shared" ref="Q264:Q271" si="15">(E264-E257)/E257</f>
+        <v>-2.3952111246191552E-3</v>
+      </c>
+      <c r="R264" s="20">
+        <f t="shared" ref="R264:R271" si="16">(F264-F257)/F257</f>
+        <v>1.810047892161106E-3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" ht="22" customHeight="1">
+      <c r="A265" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="B265" s="13">
+        <v>200341861967</v>
+      </c>
+      <c r="C265" s="13">
+        <v>203757907022</v>
+      </c>
+      <c r="D265" s="13">
+        <v>3416045055</v>
+      </c>
+      <c r="E265" s="13">
+        <v>6490250</v>
+      </c>
+      <c r="F265" s="13">
+        <v>3833547</v>
+      </c>
+      <c r="G265" s="13">
+        <v>53151</v>
+      </c>
+      <c r="H265" s="13">
+        <v>31394</v>
+      </c>
+      <c r="I265" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J265" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K265" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="L265" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="M265" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="N265" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="O265" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="P265" s="20">
+        <f t="shared" si="14"/>
+        <v>-7.8679726101755429E-2</v>
+      </c>
+      <c r="Q265" s="20">
+        <f t="shared" si="15"/>
+        <v>-6.3517204430936905E-2</v>
+      </c>
+      <c r="R265" s="20">
+        <f t="shared" si="16"/>
+        <v>-4.9799229636680001E-2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" ht="22" customHeight="1">
+      <c r="A266" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="B266" s="13">
+        <v>195313606140</v>
+      </c>
+      <c r="C266" s="13">
+        <v>198415728064</v>
+      </c>
+      <c r="D266" s="13">
+        <v>3102121924</v>
+      </c>
+      <c r="E266" s="13">
+        <v>6274203</v>
+      </c>
+      <c r="F266" s="13">
+        <v>3774197</v>
+      </c>
+      <c r="G266" s="13">
+        <v>52572</v>
+      </c>
+      <c r="H266" s="13">
+        <v>31624</v>
+      </c>
+      <c r="I266" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J266" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K266" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="L266" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="M266" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N266" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="O266" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="P266" s="20">
+        <f t="shared" si="14"/>
+        <v>-5.6303229301670234E-2</v>
+      </c>
+      <c r="Q266" s="20">
+        <f t="shared" si="15"/>
+        <v>-6.1163643578733183E-2</v>
+      </c>
+      <c r="R266" s="20">
+        <f t="shared" si="16"/>
+        <v>-3.0479227547543598E-2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" ht="22" customHeight="1">
+      <c r="A267" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="B267" s="13">
+        <v>191327776908</v>
+      </c>
+      <c r="C267" s="13">
+        <v>194332427154</v>
+      </c>
+      <c r="D267" s="13">
+        <v>3004650246</v>
+      </c>
+      <c r="E267" s="13">
+        <v>6109716</v>
+      </c>
+      <c r="F267" s="13">
+        <v>3688291</v>
+      </c>
+      <c r="G267" s="13">
+        <v>52689</v>
+      </c>
+      <c r="H267" s="13">
+        <v>31807</v>
+      </c>
+      <c r="I267" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J267" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K267" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="L267" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M267" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="N267" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="O267" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="P267" s="20">
+        <f t="shared" si="14"/>
+        <v>-5.4830319597624452E-2</v>
+      </c>
+      <c r="Q267" s="20">
+        <f t="shared" si="15"/>
+        <v>-6.7743272333545532E-2</v>
+      </c>
+      <c r="R267" s="20">
+        <f t="shared" si="16"/>
+        <v>-4.0986031950742602E-2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" ht="22" customHeight="1">
+      <c r="A268" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="B268" s="13">
+        <v>181124288502</v>
+      </c>
+      <c r="C268" s="13">
+        <v>184234507945</v>
+      </c>
+      <c r="D268" s="13">
+        <v>3110219443</v>
+      </c>
+      <c r="E268" s="13">
+        <v>5859894</v>
+      </c>
+      <c r="F268" s="13">
+        <v>3550632</v>
+      </c>
+      <c r="G268" s="13">
+        <v>51888</v>
+      </c>
+      <c r="H268" s="13">
+        <v>31440</v>
+      </c>
+      <c r="I268" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J268" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K268" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L268" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="M268" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="N268" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="O268" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="P268" s="20">
+        <f t="shared" si="14"/>
+        <v>-2.809118479210947E-2</v>
+      </c>
+      <c r="Q268" s="20">
+        <f t="shared" si="15"/>
+        <v>-1.9305963999509977E-2</v>
+      </c>
+      <c r="R268" s="20">
+        <f t="shared" si="16"/>
+        <v>-1.1870471763171648E-2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" ht="22" customHeight="1">
+      <c r="A269" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B269" s="13">
+        <v>145626186730</v>
+      </c>
+      <c r="C269" s="13">
+        <v>148007871450</v>
+      </c>
+      <c r="D269" s="13">
+        <v>2381684720</v>
+      </c>
+      <c r="E269" s="13">
+        <v>4867790</v>
+      </c>
+      <c r="F269" s="13">
+        <v>3311453</v>
+      </c>
+      <c r="G269" s="13">
+        <v>44696</v>
+      </c>
+      <c r="H269" s="13">
+        <v>30406</v>
+      </c>
+      <c r="I269" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J269" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K269" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="L269" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="M269" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="N269" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="O269" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="P269" s="20">
+        <f t="shared" si="14"/>
+        <v>-2.34095721283414E-2</v>
+      </c>
+      <c r="Q269" s="20">
+        <f t="shared" si="15"/>
+        <v>9.4058370145679634E-3</v>
+      </c>
+      <c r="R269" s="20">
+        <f t="shared" si="16"/>
+        <v>3.6543052122267228E-3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" ht="22" customHeight="1">
+      <c r="A270" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="B270" s="13">
+        <v>153832900840</v>
+      </c>
+      <c r="C270" s="13">
+        <v>155893807275</v>
+      </c>
+      <c r="D270" s="13">
+        <v>2060906435</v>
+      </c>
+      <c r="E270" s="13">
+        <v>5147932</v>
+      </c>
+      <c r="F270" s="13">
+        <v>3482760</v>
+      </c>
+      <c r="G270" s="13">
+        <v>44762</v>
+      </c>
+      <c r="H270" s="13">
+        <v>30283</v>
+      </c>
+      <c r="I270" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J270" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K270" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="L270" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="M270" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="N270" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="O270" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="P270" s="20">
+        <f t="shared" si="14"/>
+        <v>-2.6076495616128601E-2</v>
+      </c>
+      <c r="Q270" s="20">
+        <f t="shared" si="15"/>
+        <v>1.0415013798532097E-3</v>
+      </c>
+      <c r="R270" s="20">
+        <f t="shared" si="16"/>
+        <v>-2.9698259499921845E-3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" ht="22" customHeight="1">
+      <c r="A271" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="B271" s="13">
+        <v>208252176183</v>
+      </c>
+      <c r="C271" s="13">
+        <v>211001407747</v>
+      </c>
+      <c r="D271" s="13">
+        <v>2749231564</v>
+      </c>
+      <c r="E271" s="13">
+        <v>6847608</v>
+      </c>
+      <c r="F271" s="13">
+        <v>3891410</v>
+      </c>
+      <c r="G271" s="13">
+        <v>54222</v>
+      </c>
+      <c r="H271" s="13">
+        <v>30814</v>
+      </c>
+      <c r="I271" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J271" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K271" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="L271" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M271" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="N271" s="15" t="s">
+        <v>830</v>
+      </c>
+      <c r="O271" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="P271" s="20">
+        <f t="shared" si="14"/>
+        <v>-4.0393204091784894E-2</v>
+      </c>
+      <c r="Q271" s="20">
+        <f t="shared" si="15"/>
+        <v>-1.6872202580714632E-2</v>
+      </c>
+      <c r="R271" s="20">
+        <f t="shared" si="16"/>
+        <v>-2.2534105343695907E-2</v>
       </c>
     </row>
   </sheetData>
